--- a/results/job_matches_2026-07-24.xlsx
+++ b/results/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G174"/>
+  <dimension ref="A1:G184"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2708,25 +2708,25 @@
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Continuum Media Network Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
+          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
+          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,19 +2806,19 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
+          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -2827,11 +2827,11 @@
         </is>
       </c>
       <c r="D69" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc1bf7c13d30efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Sr JAVA Full Stack - Lake Mary, FL (Onsite)</t>
+          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0071b97226cb4875</t>
+          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Sr JAVA Full Stack - Lake Mary, FL (Onsite)</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3d3af2808d31529e</t>
+          <t>https://www.indeed.com/viewjob?jk=cc1bf7c13d30efa0</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote Opportunity)</t>
+          <t>Sr JAVA Full Stack - Lake Mary, FL (Onsite)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Universal Background Screening</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,69 +2936,69 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b2caf1308dae3d</t>
+          <t>https://www.indeed.com/viewjob?jk=0071b97226cb4875</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Ad Serving</t>
+          <t>Software Engineer (Remote Opportunity)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Universal Background Screening</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Phoenix, AZ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
+          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
+          <t>https://www.indeed.com/viewjob?jk=b6b2caf1308dae3d</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Platform Engineer IV</t>
+          <t>Senior Data Engineer - Ad Serving</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
+          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer IV</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Infotron</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3ab05c9087dbd4</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Quality Analyst</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BBQ Holdings</t>
+          <t>Infotron</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Berkeley, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,7 +3086,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
+          <t>https://www.indeed.com/viewjob?jk=fa3ab05c9087dbd4</t>
         </is>
       </c>
     </row>
@@ -3098,12 +3098,12 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Kahala Management LLC</t>
+          <t>BBQ Holdings</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Scottsdale, AZ, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3116,29 +3116,29 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a5698b7be59595f7</t>
+          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Gen. AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bagel Brands</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Brooklyn Center, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,42 +3146,42 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
+          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Acquisition</t>
+          <t>Gen. AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>People Data Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,24 +3191,24 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
+          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Software Engineer, Data Acquisition</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>People Data Labs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,7 +3216,7 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
+          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
         </is>
       </c>
     </row>
@@ -3278,7 +3278,7 @@
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior QA Engineer - Airvoyant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Coral Gables, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
+          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82cedf3a5c098bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>DevOps Engineer</t>
+          <t>Senior QA Engineer - Airvoyant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Rippling</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Coral Gables, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, IAM, RDS, Scala, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,32 +3401,32 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6e8b25e2f2a2f9a</t>
+          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Scientist Senior Associate</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Antonio, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,7 +3436,7 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b26575de63e016</t>
+          <t>https://www.indeed.com/viewjob?jk=a82cedf3a5c098bf</t>
         </is>
       </c>
     </row>
@@ -3453,7 +3453,7 @@
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3471,19 +3471,19 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d4db52b41a4c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b26575de63e016</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Finance Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>IFS</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,19 +3506,19 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
+          <t>https://www.indeed.com/viewjob?jk=22d4db52b41a4c7e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AI/ML Platform Engineer</t>
+          <t>Senior Finance Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Mercedes-Benz Group</t>
+          <t>IFS</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, Spark, PySpark, Scala, ELT, MLOps</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=acd1f12311583f7b</t>
+          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Azure Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>CSpring</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Indianapolis, IN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,17 +3566,17 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Spark, PySpark, Data Modeling, Dimensional Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0cb38eb50869058</t>
+          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
         </is>
       </c>
     </row>
@@ -3828,17 +3828,17 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
+          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
+          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Northramp</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe02b7c8ca17adb</t>
+          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Optimum Data Modeler - BSS Transformation</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Northramp</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
+          <t>https://www.indeed.com/viewjob?jk=8fe02b7c8ca17adb</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Engineer – AI &amp; Machine Learning</t>
+          <t>Optimum Data Modeler - BSS Transformation</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, NoSQL, ETL, MLOps, CI/CD, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426013248af00194</t>
+          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer, Structured Storage</t>
+          <t>Software Engineer – AI &amp; Machine Learning</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, Splunk</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, NoSQL, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffb8f2b64505893</t>
+          <t>https://www.indeed.com/viewjob?jk=426013248af00194</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Remote</t>
+          <t>Software Engineer, Structured Storage</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, Splunk</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=985f073bd5ef4e60</t>
+          <t>https://www.indeed.com/viewjob?jk=2ffb8f2b64505893</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Enterprise Data Integration &amp; Migration Senior Associate</t>
+          <t>Sr. Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8e3aded50f9da6</t>
+          <t>https://www.indeed.com/viewjob?jk=985f073bd5ef4e60</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Enterprise Data Integration &amp; Migration Senior Associate</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,17 +4126,17 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1296ebd08a57d7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8e3aded50f9da6</t>
         </is>
       </c>
     </row>
@@ -4153,7 +4153,7 @@
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4171,32 +4171,32 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb71d7121f8589</t>
+          <t>https://www.indeed.com/viewjob?jk=1296ebd08a57d7ad</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Workday Everywhere</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,32 +4206,32 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb71d7121f8589</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,24 +4241,24 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cronisys IT LLC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,34 +4266,34 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
+          <t>https://www.indeed.com/viewjob?jk=c38a539ce614bcac</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Cronisys IT LLC</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,34 +4301,34 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Software Development Engineer - Workday Everywhere</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,7 +4336,7 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,24 +4346,24 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893e910c3bd5c112</t>
+          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0141781c1f467720</t>
+          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c7d8075142645e</t>
+          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Software Engineer III - PA085</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
+          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Research Triangle Park, NC, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b234271097cd37b1</t>
+          <t>https://www.indeed.com/viewjob?jk=893e910c3bd5c112</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Senior Big Data Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Magnite</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Benson, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc450b1d33691a</t>
+          <t>https://www.indeed.com/viewjob?jk=0141781c1f467720</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Software Engineer 3</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, Docker</t>
+          <t>AWS, Spark, Scala, Kafka, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc906c390155312</t>
+          <t>https://www.indeed.com/viewjob?jk=41c7d8075142645e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57865e75c379265</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f8300de4fecb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - PA085</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45adc4c2b25c26f7</t>
+          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Analytics Platform</t>
+          <t>Applied Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
+          <t>https://www.indeed.com/viewjob?jk=b234271097cd37b1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
+          <t>Applied Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Egen Solutions Inc</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Benson, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc450b1d33691a</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc906c390155312</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,7 +4826,7 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
+          <t>https://www.indeed.com/viewjob?jk=f57865e75c379265</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Irving, TX, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1feab28b0c3d3479</t>
+          <t>https://www.indeed.com/viewjob?jk=55f8300de4fecb0f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Software Engineer 1 (React + API + Cloud Migration)</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>U.S. Bank</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,42 +4896,42 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, PostgreSQL, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c64848853e9c5d68</t>
+          <t>https://www.indeed.com/viewjob?jk=45adc4c2b25c26f7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Engineer - Analytics Platform</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
+          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
+          <t>https://www.indeed.com/viewjob?jk=5777ab28ff195025</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Egen Solutions Inc</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
+          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kyocera Document Solutions America, Inc.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Fairfield, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
+          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,14 +5221,14 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
+          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
+          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,14 +5326,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
+          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
+          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,7 +5396,7 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
         </is>
       </c>
     </row>
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,14 +5431,14 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,14 +5466,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
+          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,24 +5641,24 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr. Associate Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5666,7 +5666,7 @@
       </c>
       <c r="E150" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F150" t="inlineStr">
@@ -5676,24 +5676,24 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
+          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5701,7 +5701,7 @@
       </c>
       <c r="E151" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F151" t="inlineStr">
@@ -5711,24 +5711,24 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5736,7 +5736,7 @@
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
@@ -5746,24 +5746,24 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
+          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
         <is>
-          <t>INROADS</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5771,7 +5771,7 @@
       </c>
       <c r="E153" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F153" t="inlineStr">
@@ -5781,24 +5781,24 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>Bevi</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Charlestown, MA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5806,7 +5806,7 @@
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, AKS</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F154" t="inlineStr">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
+          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>merican Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e555efa8f72b69a</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, dbt, AWS CloudFormation, Git, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541fc9f247e24d24</t>
+          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Sr. Associate Data Engineer</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
+          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,19 +5991,19 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
+          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>INROADS</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
+          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Bevi</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Charlestown, MA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
+          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>merican Inc</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
+          <t>https://www.indeed.com/viewjob?jk=0e555efa8f72b69a</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Data Engineer - ITS4</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>State of Minnesota - Minnesota IT Services</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Saint Paul, MN, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, dbt, AWS CloudFormation, Git, Python</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
+          <t>https://www.indeed.com/viewjob?jk=541fc9f247e24d24</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Senior AI Driven Test Automation Architect</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
+          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>IT Database Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kuehne+Nagel</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Naugatuck, CT, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f91c24f3a7633e7</t>
+          <t>https://www.indeed.com/viewjob?jk=9c73cae1a3da2412</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Senior MuleSoft Developer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Oracle, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Maven</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d311b8910fe0706e</t>
+          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Sona</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
+          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
+          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Senior Java Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
+          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Java Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>IT Architect - Cloud Platform</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ea6fc2defb727</t>
+          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, ELT, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6b13a7348518f4</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Associate Developer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Bealls Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,15 +6506,365 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Software Engineer</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>Sona</t>
+        </is>
+      </c>
+      <c r="C175" t="inlineStr">
+        <is>
+          <t>Miami, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D175" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E175" t="inlineStr">
+        <is>
+          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
+        </is>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Java Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C176" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D176" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E176" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G176" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Senior Java Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C177" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D177" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E177" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G177" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Senior Java Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C178" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D178" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E178" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G178" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Java Platform Engineer</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>Capgemini</t>
+        </is>
+      </c>
+      <c r="C179" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D179" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E179" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G179" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Quality Assurance Specialist</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>RELI Group Inc</t>
+        </is>
+      </c>
+      <c r="C180" t="inlineStr">
+        <is>
+          <t>Baltimore, MD, US USA</t>
+        </is>
+      </c>
+      <c r="D180" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E180" t="inlineStr">
+        <is>
+          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+        </is>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G180" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C181" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D181" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G181" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f91c24f3a7633e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>IT Architect - Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>Maximus</t>
+        </is>
+      </c>
+      <c r="C182" t="inlineStr">
+        <is>
+          <t>Tysons, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D182" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E182" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G182" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef9ea6fc2defb727</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>Senior Systems Engineer</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>Rocket</t>
+        </is>
+      </c>
+      <c r="C183" t="inlineStr">
+        <is>
+          <t>Detroit, MI, US USA</t>
+        </is>
+      </c>
+      <c r="D183" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E183" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, GCP, ETL, ELT, CI/CD, Terraform, Docker, Kubernetes</t>
+        </is>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>2026-07-22</t>
+        </is>
+      </c>
+      <c r="G183" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=1b6b13a7348518f4</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>Associate Developer</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>Bealls Inc.</t>
+        </is>
+      </c>
+      <c r="C184" t="inlineStr">
+        <is>
+          <t>Bradenton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D184" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E184" t="inlineStr">
+        <is>
           <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
-      <c r="F174" t="inlineStr">
+      <c r="F184" t="inlineStr">
         <is>
           <t>2026-06-17</t>
         </is>
       </c>
-      <c r="G174" t="inlineStr">
+      <c r="G184" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=723d8dc3606ce87f</t>
         </is>

--- a/results/job_matches_2026-07-24.xlsx
+++ b/results/job_matches_2026-07-24.xlsx
@@ -923,52 +923,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>19.4</v>
+        <v>18.1</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Hadoop, Spark, Scala, Kafka, Snowflake, Oracle, MongoDB</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dd1589aadea1bbd4</t>
+          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
+          <t>https://www.indeed.com/viewjob?jk=5f87cbef2e8672c3</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f87cbef2e8672c3</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0ffa581a9806f2</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0ffa581a9806f2</t>
+          <t>https://www.indeed.com/viewjob?jk=a371c6a757e7cc60</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a371c6a757e7cc60</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c4dc88ae61fe0e</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c4dc88ae61fe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=f214eae45940a168</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f214eae45940a168</t>
+          <t>https://www.indeed.com/viewjob?jk=2687a24e7dad6780</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2687a24e7dad6780</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba2e28b0686e652</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba2e28b0686e652</t>
+          <t>https://www.indeed.com/viewjob?jk=4555ac252f371341</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4555ac252f371341</t>
+          <t>https://www.indeed.com/viewjob?jk=1c21907825eebf4e</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c21907825eebf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=7237946dfe0583b2</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7237946dfe0583b2</t>
+          <t>https://www.indeed.com/viewjob?jk=801bb2fc81ed28a7</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801bb2fc81ed28a7</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca8ef229b1532c4</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca8ef229b1532c4</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6085a67377b69f</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6085a67377b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=b7352e9be8f48d42</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7352e9be8f48d42</t>
+          <t>https://www.indeed.com/viewjob?jk=95dee7b8fef58b1e</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95dee7b8fef58b1e</t>
+          <t>https://www.indeed.com/viewjob?jk=630ac099235fbd6d</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630ac099235fbd6d</t>
+          <t>https://www.indeed.com/viewjob?jk=1279bb37e0c78ee9</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1279bb37e0c78ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=02f7accbf789b4d1</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f7accbf789b4d1</t>
+          <t>https://www.indeed.com/viewjob?jk=2875a726636cc149</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2875a726636cc149</t>
+          <t>https://www.indeed.com/viewjob?jk=44506379a420841e</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44506379a420841e</t>
+          <t>https://www.indeed.com/viewjob?jk=1f29091cd781df40</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f29091cd781df40</t>
+          <t>https://www.indeed.com/viewjob?jk=02feacdf4669a553</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02feacdf4669a553</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1b6022ed0acfd4</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1b6022ed0acfd4</t>
+          <t>https://www.indeed.com/viewjob?jk=efeae60730c199e0</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efeae60730c199e0</t>
+          <t>https://www.indeed.com/viewjob?jk=2460ff417a265bbe</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2460ff417a265bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1f6380a3c4f83b</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1f6380a3c4f83b</t>
+          <t>https://www.indeed.com/viewjob?jk=9685333ed2d00ca8</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9685333ed2d00ca8</t>
+          <t>https://www.indeed.com/viewjob?jk=21091337a312c8c7</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21091337a312c8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=f893c944d1eaefab</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f893c944d1eaefab</t>
+          <t>https://www.indeed.com/viewjob?jk=cbf8f230bc8b0c83</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbf8f230bc8b0c83</t>
+          <t>https://www.indeed.com/viewjob?jk=cda9596586f3e32a</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cda9596586f3e32a</t>
+          <t>https://www.indeed.com/viewjob?jk=20b5df003b7622a9</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b5df003b7622a9</t>
+          <t>https://www.indeed.com/viewjob?jk=e8cd995cbc9be6f9</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8cd995cbc9be6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e4df8e6b664967</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e4df8e6b664967</t>
+          <t>https://www.indeed.com/viewjob?jk=fa44bcb3004b69d1</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa44bcb3004b69d1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0edbe0ca17f71c</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0edbe0ca17f71c</t>
+          <t>https://www.indeed.com/viewjob?jk=833ff84fdbb1abd1</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833ff84fdbb1abd1</t>
+          <t>https://www.indeed.com/viewjob?jk=fbac48f07a9842df</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbac48f07a9842df</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb1052d07321fc8</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb1052d07321fc8</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2fb4708a4607c9</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2fb4708a4607c9</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0e9e73889131e2</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0e9e73889131e2</t>
+          <t>https://www.indeed.com/viewjob?jk=176b93f1cf5124ab</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b93f1cf5124ab</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8bd386e42843b</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8bd386e42843b</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e471cdb7ea8fe2</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e471cdb7ea8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=a6ad11f79e7ed4e9</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ad11f79e7ed4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8935b313a478ee</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8935b313a478ee</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7a4e1799edd25d</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7a4e1799edd25d</t>
+          <t>https://www.indeed.com/viewjob?jk=7928d8310dc94518</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7928d8310dc94518</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1f237216b5ebbe</t>
         </is>
       </c>
     </row>
@@ -2678,20 +2678,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Continuum Media Network Inc</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1f237216b5ebbe</t>
+          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Continuum Media Network Inc</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
+          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Aurora, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
+          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
         </is>
       </c>
     </row>
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
+          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
+          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
         </is>
       </c>
     </row>
@@ -3128,17 +3128,17 @@
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineerâ€“ Full Stack</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bagel Brands</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brooklyn Center, MN, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
+          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Gen. AI Engineer</t>
+          <t>Senior Software Developer, Automation</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
+          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Acquisition</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>People Data Labs</t>
+          <t>Bagel Brands</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Brooklyn Center, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
+          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Gen. AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
+          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Acquisition</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>People Data Labs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
+          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior QA Engineer - Airvoyant</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Coral Gables, FL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
+          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Scientist Senior Associate</t>
+          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>San Antonio, TX, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Glue, ECS, RDS, Spark, PySpark, Oracle, ETL, Splunk, CI/CD</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,32 +3436,32 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a82cedf3a5c098bf</t>
+          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior QA Engineer - Airvoyant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Coral Gables, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b26575de63e016</t>
+          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d4db52b41a4c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Finance Data Engineer</t>
+          <t>AWS/EKS Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>IFS</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,24 +3541,24 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b26575de63e016</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d53fa67d1e5eb8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=22d4db52b41a4c7e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Senior Finance Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>New York City Department of Citywide Administrative Services</t>
+          <t>IFS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, Azure Cosmos DB, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8959b284cfe01ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Software Engineer - 3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
+          <t>https://www.indeed.com/viewjob?jk=d53fa67d1e5eb8e1</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>AWS Cloud AI Engineer</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>New York City Department of Citywide Administrative Services</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, Azure Cosmos DB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=8959b284cfe01ae8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>AI/ML Ops and Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
+          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Machine Learning Ops Data Engineer</t>
+          <t>Software Engineer - 3</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
+          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Data engineer with Java</t>
+          <t>AWS Cloud AI Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, ECS, RDS, Cloud Storage, Scala, ETL</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40731666819fe80</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE)</t>
+          <t>AI/ML Ops and Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Machine Learning Ops Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
+          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data engineer with Java</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, ECS, RDS, Cloud Storage, Scala, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
+          <t>https://www.indeed.com/viewjob?jk=b40731666819fe80</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Full Stack Developer</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Northramp</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Kafka, CI/CD, Jenkins, GitHub Actions</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8fe02b7c8ca17adb</t>
+          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Optimum Data Modeler - BSS Transformation</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
+          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Engineer – AI &amp; Machine Learning</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, NoSQL, ETL, MLOps, CI/CD, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426013248af00194</t>
+          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Engineer, Structured Storage</t>
+          <t>Optimum Data Modeler - BSS Transformation</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, NoSQL, Data Modeling, Splunk</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2ffb8f2b64505893</t>
+          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Remote</t>
+          <t>Software Engineer – AI &amp; Machine Learning</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Veryon</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, NoSQL, ETL, MLOps, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,24 +4101,24 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=985f073bd5ef4e60</t>
+          <t>https://www.indeed.com/viewjob?jk=426013248af00194</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Enterprise Data Integration &amp; Migration Senior Associate</t>
+          <t>Sr. Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8e3aded50f9da6</t>
+          <t>https://www.indeed.com/viewjob?jk=985f073bd5ef4e60</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Enterprise Data Integration &amp; Migration Senior Associate</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,17 +4161,17 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1296ebd08a57d7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8e3aded50f9da6</t>
         </is>
       </c>
     </row>
@@ -4188,7 +4188,7 @@
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb71d7121f8589</t>
+          <t>https://www.indeed.com/viewjob?jk=1296ebd08a57d7ad</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,94 +4241,94 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb71d7121f8589</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cronisys IT LLC</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c38a539ce614bcac</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Solutions Architect | US</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cronisys IT LLC</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Workday Everywhere</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Cronisys IT LLC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Software Development Engineer - Workday Everywhere</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
+          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
+          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Research Triangle Park, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Scala, PostgreSQL, NoSQL, Splunk, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,24 +4486,24 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=893e910c3bd5c112</t>
+          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Senior Big Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Magnite</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,34 +4511,34 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, Hadoop, Spark, Scala, Kafka, PostgreSQL, MySQL, CI/CD, Terraform, Kubernetes</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0141781c1f467720</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Software Engineer 3</t>
+          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Spark, Scala, Kafka, NoSQL, ETL, Jenkins, Docker, Kubernetes, Jenkins</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=41c7d8075142645e</t>
+          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Software Engineer III - PA085</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,34 +4581,34 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
+          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
+          <t>Applied Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=b234271097cd37b1</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer III - PA085</t>
+          <t>Applied Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Benson, NC, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc450b1d33691a</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b234271097cd37b1</t>
+          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Benson, NC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc450b1d33691a</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc906c390155312</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=f57865e75c379265</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc906c390155312</t>
+          <t>https://www.indeed.com/viewjob?jk=55f8300de4fecb0f</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57865e75c379265</t>
+          <t>https://www.indeed.com/viewjob?jk=45adc4c2b25c26f7</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer - Analytics Platform</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f8300de4fecb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45adc4c2b25c26f7</t>
+          <t>https://www.indeed.com/viewjob?jk=5777ab28ff195025</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Analytics Platform</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5777ab28ff195025</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>Egen Solutions Inc</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
+          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Egen Solutions Inc</t>
+          <t>Kyocera Document Solutions America, Inc.</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Fairfield, NJ, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
+          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Kyocera Document Solutions America, Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Fairfield, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,7 +5151,7 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
         </is>
       </c>
     </row>
@@ -5168,7 +5168,7 @@
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5186,14 +5186,14 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
+          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
+          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
+          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,7 +5291,7 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
         </is>
       </c>
     </row>
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,14 +5326,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
+          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
+          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,14 +5466,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
+          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,14 +5606,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
+          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,7 +5641,7 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
+          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
         </is>
       </c>
     </row>
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
+          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
+          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Associate Data Engineer</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sr. Associate Data Engineer</t>
+          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
+          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>INROADS</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
+          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Bevi</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Charlestown, MA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
+          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>INROADS</t>
+          <t>merican Inc</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=0e555efa8f72b69a</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Bevi</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Charlestown, MA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, AKS</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
+          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>merican Inc</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e555efa8f72b69a</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Data Engineer - ITS4</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>State of Minnesota - Minnesota IT Services</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Saint Paul, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, NoSQL, dbt, AWS CloudFormation, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,7 +6131,7 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=541fc9f247e24d24</t>
+          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
         </is>
       </c>
     </row>
@@ -6208,7 +6208,7 @@
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
@@ -6218,7 +6218,7 @@
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
+          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Sona</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Software Engineer – Remote Opportunities</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
+          <t>https://www.indeed.com/viewjob?jk=a59520fbf843f452</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
+          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Senior Java Platform Engineer</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
+          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Senior Java Platform Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
+          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Quality Assurance Specialist</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
+          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>IT Architect - Cloud Platform</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9ea6fc2defb727</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Associate Developer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Sona</t>
+          <t>Bealls Inc.</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,34 +6541,34 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
+          <t>https://www.indeed.com/viewjob?jk=723d8dc3606ce87f</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
+          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Java Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
+          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Senior Java Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
+          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Quality Assurance Specialist</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f91c24f3a7633e7</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>IT Architect - Cloud Platform</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,7 +6786,7 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
@@ -6796,24 +6796,24 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ea6fc2defb727</t>
+          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
         </is>
       </c>
     </row>
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
         <is>
-          <t>Rocket</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Detroit, MI, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6821,34 +6821,34 @@
       </c>
       <c r="E183" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, ETL, ELT, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F183" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1b6b13a7348518f4</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
         </is>
       </c>
     </row>
     <row r="184">
       <c r="A184" t="inlineStr">
         <is>
-          <t>Associate Developer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B184" t="inlineStr">
         <is>
-          <t>Bealls Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6856,17 +6856,17 @@
       </c>
       <c r="E184" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F184" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=723d8dc3606ce87f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f91c24f3a7633e7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-24.xlsx
+++ b/results/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G184"/>
+  <dimension ref="A1:G188"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2953,52 +2953,52 @@
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer (Remote Opportunity)</t>
+          <t>Senior Data Engineer - Ad Serving</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Universal Background Screening</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Phoenix, AZ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, S3, RDS, Azure, Scala, SQL Server, PostgreSQL</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6b2caf1308dae3d</t>
+          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Ad Serving</t>
+          <t>Platform Engineer IV</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Platform Engineer IV</t>
+          <t>Data Quality Analyst</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>BBQ Holdings</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
+          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineerâ€“ Full Stack</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Infotron</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Berkeley, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Scala, PostgreSQL, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa3ab05c9087dbd4</t>
+          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Quality Analyst</t>
+          <t>Senior Software Developer, Automation</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BBQ Holdings</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
+          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineerâ€“ Full Stack</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Bagel Brands</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Brooklyn Center, MN, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
+          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Developer, Automation</t>
+          <t>Gen. AI Engineer</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,7 +3181,7 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
+          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Engineer, Data Acquisition</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bagel Brands</t>
+          <t>People Data Labs</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brooklyn Center, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Gen. AI Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD, Jenkins</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
+          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Acquisition</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>People Data Labs</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
+          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
+          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
+          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior QA Engineer - Airvoyant</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Coral Gables, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
+          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior QA Engineer - Airvoyant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Coral Gables, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,24 +3471,24 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
+          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>AWS/EKS Platform Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS/EKS Platform Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b26575de63e016</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b26575de63e016</t>
+          <t>https://www.indeed.com/viewjob?jk=22d4db52b41a4c7e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Finance Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>IFS</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d4db52b41a4c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Finance Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IFS</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
+          <t>https://www.indeed.com/viewjob?jk=d53fa67d1e5eb8e1</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d53fa67d1e5eb8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
         </is>
       </c>
     </row>
@@ -3723,25 +3723,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Software Engineer - 3</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
+          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer - 3</t>
+          <t>AWS Cloud AI Engineer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AWS Cloud AI Engineer</t>
+          <t>AI/ML Ops and Data Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI/ML Ops and Data Engineer</t>
+          <t>Machine Learning Ops Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
+          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Machine Learning Ops Data Engineer</t>
+          <t>Data engineer with Java</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, ECS, RDS, Cloud Storage, Scala, ETL</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
+          <t>https://www.indeed.com/viewjob?jk=b40731666819fe80</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data engineer with Java</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, ECS, RDS, Cloud Storage, Scala, ETL</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40731666819fe80</t>
+          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE)</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,7 +3961,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
+          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
         </is>
       </c>
     </row>
@@ -4003,17 +4003,17 @@
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Optimum Data Modeler - BSS Transformation</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
+          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Optimum Data Modeler - BSS Transformation</t>
+          <t>Sr. Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,59 +4066,59 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
+          <t>https://www.indeed.com/viewjob?jk=985f073bd5ef4e60</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Software Engineer – AI &amp; Machine Learning</t>
+          <t>Enterprise Data Integration &amp; Migration Senior Associate</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Veryon</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, NoSQL, ETL, MLOps, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=426013248af00194</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8e3aded50f9da6</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Remote</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,7 +4126,7 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,24 +4136,24 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=985f073bd5ef4e60</t>
+          <t>https://www.indeed.com/viewjob?jk=1296ebd08a57d7ad</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Enterprise Data Integration &amp; Migration Senior Associate</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, Snowflake Schema, ETL</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8e3aded50f9da6</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb71d7121f8589</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1296ebd08a57d7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>AI Solutions Architect | US</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,67 +4241,67 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb71d7121f8589</t>
+          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Cronisys IT LLC</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Solutions Architect | US</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
+          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer - Workday Everywhere</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cronisys IT LLC</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Workday Everywhere</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,7 +4381,7 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
+          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
         </is>
       </c>
     </row>
@@ -4398,7 +4398,7 @@
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
+          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
+          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Clinical Data Engineer (Application Engineer)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>Oregon Health &amp; Science University</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,17 +4511,17 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
+          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
         </is>
       </c>
     </row>
@@ -4668,17 +4668,17 @@
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>SW Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,34 +4721,34 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, Docker</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc906c390155312</t>
+          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57865e75c379265</t>
+          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f8300de4fecb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc906c390155312</t>
         </is>
       </c>
     </row>
@@ -4818,7 +4818,7 @@
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4836,24 +4836,24 @@
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45adc4c2b25c26f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f57865e75c379265</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Analytics Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,24 +4871,24 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
+          <t>https://www.indeed.com/viewjob?jk=55f8300de4fecb0f</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5777ab28ff195025</t>
+          <t>https://www.indeed.com/viewjob?jk=45adc4c2b25c26f7</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Analytics Platform</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
+          <t>https://www.indeed.com/viewjob?jk=5777ab28ff195025</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Egen Solutions Inc</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Kyocera Document Solutions America, Inc.</t>
+          <t>Egen Solutions Inc</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Fairfield, NJ, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,32 +5081,32 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,32 +5116,32 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kyocera Document Solutions America, Inc.</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fairfield, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,24 +5176,24 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
+          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5221,7 +5221,7 @@
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,14 +5256,14 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,14 +5291,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,7 +5326,7 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
+          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
         </is>
       </c>
     </row>
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
+          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
+          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,14 +5431,14 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,14 +5466,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
+          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
+          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,7 +5571,7 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
         </is>
       </c>
     </row>
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
+          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
+          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,14 +5746,14 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
+          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B153" t="inlineStr">
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,24 +5816,24 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="inlineStr">
         <is>
-          <t>Sr. Associate Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5841,7 +5841,7 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F155" t="inlineStr">
@@ -5851,24 +5851,24 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
+          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F156" t="inlineStr">
@@ -5886,24 +5886,24 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Associate Data Engineer</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>INROADS</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Bevi</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Charlestown, MA, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, AKS</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>merican Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e555efa8f72b69a</t>
+          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>INROADS</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
+          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Bevi</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Charlestown, MA, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
+          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>merican Inc</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
+          <t>https://www.indeed.com/viewjob?jk=0e555efa8f72b69a</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Senior AI Driven Test Automation Architect</t>
+          <t>IT Cloud Architect</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
+          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>IT Database Engineer</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>Kuehne+Nagel</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Naugatuck, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,7 +6191,7 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
@@ -6201,24 +6201,24 @@
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c73cae1a3da2412</t>
+          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Sona</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
+          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Software Engineer – Remote Opportunities</t>
+          <t>Senior AI Driven Test Automation Architect</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a59520fbf843f452</t>
+          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>IT Database Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Kuehne+Nagel</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Naugatuck, CT, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
+          <t>https://www.indeed.com/viewjob?jk=9c73cae1a3da2412</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Senior Java Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
+          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Senior Java Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sona</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Software Engineer – Remote Opportunities</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
+          <t>https://www.indeed.com/viewjob?jk=a59520fbf843f452</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Quality Assurance Specialist</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,7 +6471,7 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
@@ -6481,24 +6481,24 @@
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
+          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>IT Architect - Cloud Platform</t>
+          <t>Senior Java Platform Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ea6fc2defb727</t>
+          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Associate Developer</t>
+          <t>Senior Java Platform Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Bealls Inc.</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,34 +6541,34 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=723d8dc3606ce87f</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
+          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Quality Assurance Specialist</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
+          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
         </is>
       </c>
     </row>
@@ -6638,7 +6638,7 @@
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6656,7 +6656,7 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
+          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
         </is>
       </c>
     </row>
@@ -6673,7 +6673,7 @@
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
+          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
         </is>
       </c>
     </row>
@@ -6708,7 +6708,7 @@
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6726,7 +6726,7 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
+          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
         </is>
       </c>
     </row>
@@ -6743,7 +6743,7 @@
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
+          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
         </is>
       </c>
     </row>
@@ -6778,7 +6778,7 @@
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6796,7 +6796,7 @@
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,147 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
+          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C185" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D185" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E185" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G185" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C186" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D186" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E186" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G186" t="inlineStr">
+        <is>
           <t>https://www.indeed.com/viewjob?jk=6f91c24f3a7633e7</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>IT Architect - Cloud Platform</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>Maximus</t>
+        </is>
+      </c>
+      <c r="C187" t="inlineStr">
+        <is>
+          <t>Tysons, VA, US USA</t>
+        </is>
+      </c>
+      <c r="D187" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E187" t="inlineStr">
+        <is>
+          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+        </is>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G187" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=ef9ea6fc2defb727</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>Associate Developer</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>Bealls Inc.</t>
+        </is>
+      </c>
+      <c r="C188" t="inlineStr">
+        <is>
+          <t>Bradenton, FL, US USA</t>
+        </is>
+      </c>
+      <c r="D188" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E188" t="inlineStr">
+        <is>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+        </is>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>2026-06-17</t>
+        </is>
+      </c>
+      <c r="G188" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=723d8dc3606ce87f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-24.xlsx
+++ b/results/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G188"/>
+  <dimension ref="A1:G191"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,52 +923,52 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Software Engineer III-Databricks</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
+          <t>https://www.indeed.com/viewjob?jk=4788de97836b6e30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,7 +976,7 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f87cbef2e8672c3</t>
+          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
         </is>
       </c>
     </row>
@@ -1003,7 +1003,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0ffa581a9806f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5f87cbef2e8672c3</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a371c6a757e7cc60</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0ffa581a9806f2</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c4dc88ae61fe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=a371c6a757e7cc60</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f214eae45940a168</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c4dc88ae61fe0e</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2687a24e7dad6780</t>
+          <t>https://www.indeed.com/viewjob?jk=f214eae45940a168</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba2e28b0686e652</t>
+          <t>https://www.indeed.com/viewjob?jk=2687a24e7dad6780</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4555ac252f371341</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba2e28b0686e652</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c21907825eebf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=4555ac252f371341</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7237946dfe0583b2</t>
+          <t>https://www.indeed.com/viewjob?jk=1c21907825eebf4e</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801bb2fc81ed28a7</t>
+          <t>https://www.indeed.com/viewjob?jk=7237946dfe0583b2</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca8ef229b1532c4</t>
+          <t>https://www.indeed.com/viewjob?jk=801bb2fc81ed28a7</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6085a67377b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca8ef229b1532c4</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7352e9be8f48d42</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6085a67377b69f</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95dee7b8fef58b1e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7352e9be8f48d42</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630ac099235fbd6d</t>
+          <t>https://www.indeed.com/viewjob?jk=95dee7b8fef58b1e</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1279bb37e0c78ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=630ac099235fbd6d</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f7accbf789b4d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1279bb37e0c78ee9</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2875a726636cc149</t>
+          <t>https://www.indeed.com/viewjob?jk=02f7accbf789b4d1</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44506379a420841e</t>
+          <t>https://www.indeed.com/viewjob?jk=2875a726636cc149</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f29091cd781df40</t>
+          <t>https://www.indeed.com/viewjob?jk=44506379a420841e</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02feacdf4669a553</t>
+          <t>https://www.indeed.com/viewjob?jk=1f29091cd781df40</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1b6022ed0acfd4</t>
+          <t>https://www.indeed.com/viewjob?jk=02feacdf4669a553</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efeae60730c199e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1b6022ed0acfd4</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2460ff417a265bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=efeae60730c199e0</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1f6380a3c4f83b</t>
+          <t>https://www.indeed.com/viewjob?jk=2460ff417a265bbe</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9685333ed2d00ca8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1f6380a3c4f83b</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21091337a312c8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9685333ed2d00ca8</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f893c944d1eaefab</t>
+          <t>https://www.indeed.com/viewjob?jk=21091337a312c8c7</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbf8f230bc8b0c83</t>
+          <t>https://www.indeed.com/viewjob?jk=f893c944d1eaefab</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cda9596586f3e32a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbf8f230bc8b0c83</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b5df003b7622a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cda9596586f3e32a</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8cd995cbc9be6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=20b5df003b7622a9</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e4df8e6b664967</t>
+          <t>https://www.indeed.com/viewjob?jk=e8cd995cbc9be6f9</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa44bcb3004b69d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e4df8e6b664967</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0edbe0ca17f71c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa44bcb3004b69d1</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833ff84fdbb1abd1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0edbe0ca17f71c</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbac48f07a9842df</t>
+          <t>https://www.indeed.com/viewjob?jk=833ff84fdbb1abd1</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb1052d07321fc8</t>
+          <t>https://www.indeed.com/viewjob?jk=fbac48f07a9842df</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2fb4708a4607c9</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb1052d07321fc8</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0e9e73889131e2</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2fb4708a4607c9</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b93f1cf5124ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0e9e73889131e2</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8bd386e42843b</t>
+          <t>https://www.indeed.com/viewjob?jk=176b93f1cf5124ab</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e471cdb7ea8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8bd386e42843b</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ad11f79e7ed4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e471cdb7ea8fe2</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8935b313a478ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a6ad11f79e7ed4e9</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7a4e1799edd25d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8935b313a478ee</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7928d8310dc94518</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7a4e1799edd25d</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1f237216b5ebbe</t>
+          <t>https://www.indeed.com/viewjob?jk=7928d8310dc94518</t>
         </is>
       </c>
     </row>
@@ -2678,20 +2678,20 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Continuum Media Network Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
+          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1f237216b5ebbe</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>Continuum Media Network Inc</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Aurora, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
+          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,7 +2771,7 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
+          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
         </is>
       </c>
     </row>
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
+          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,32 +2841,32 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
+          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
+          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
+          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc1bf7c13d30efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Sr JAVA Full Stack - Lake Mary, FL (Onsite)</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0071b97226cb4875</t>
+          <t>https://www.indeed.com/viewjob?jk=cc1bf7c13d30efa0</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Ad Serving</t>
+          <t>Sr JAVA Full Stack - Lake Mary, FL (Onsite)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
+          <t>https://www.indeed.com/viewjob?jk=0071b97226cb4875</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Platform Engineer IV</t>
+          <t>Senior Data Engineer - Ad Serving</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
+          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Data Quality Analyst</t>
+          <t>Platform Engineer IV</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>BBQ Holdings</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Software Engineerâ€“ Full Stack</t>
+          <t>Data Quality Analyst</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>BBQ Holdings</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
+          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Software Developer, Automation</t>
+          <t>Software Engineerâ€“ Full Stack</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,7 +3111,7 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
+          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Developer, Automation</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Bagel Brands</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Brooklyn Center, MN, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,34 +3146,34 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
+          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Gen. AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bagel Brands</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Brooklyn Center, MN, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,42 +3181,42 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
+          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Acquisition</t>
+          <t>Gen. AI Engineer</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>People Data Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
@@ -3226,24 +3226,24 @@
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
+          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Software Engineer, Data Acquisition</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>People Data Labs</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
@@ -3251,7 +3251,7 @@
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,7 +3296,7 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
+          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
         </is>
       </c>
     </row>
@@ -3313,7 +3313,7 @@
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3331,24 +3331,24 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3356,7 +3356,7 @@
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
+          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Senior QA Engineer - Airvoyant</t>
+          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Coral Gables, FL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,59 +3401,59 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
+          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior QA Engineer - Airvoyant</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Coral Gables, FL, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,34 +3461,34 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>AWS/EKS Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,7 +3496,7 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
@@ -3506,24 +3506,24 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS/EKS Platform Engineer</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,7 +3531,7 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
@@ -3541,7 +3541,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b26575de63e016</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
         </is>
       </c>
     </row>
@@ -3558,7 +3558,7 @@
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3576,19 +3576,19 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d4db52b41a4c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b26575de63e016</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Finance Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>IFS</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
+          <t>https://www.indeed.com/viewjob?jk=22d4db52b41a4c7e</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Finance Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>IFS</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d53fa67d1e5eb8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,7 +3681,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
+          <t>https://www.indeed.com/viewjob?jk=d53fa67d1e5eb8e1</t>
         </is>
       </c>
     </row>
@@ -3723,25 +3723,25 @@
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Software Engineer - 3</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,24 +3751,24 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
+          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>AWS Cloud AI Engineer</t>
+          <t>Software Engineer - 3</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
@@ -3776,7 +3776,7 @@
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,24 +3786,24 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AI/ML Ops and Data Engineer</t>
+          <t>AWS Cloud AI Engineer</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
@@ -3811,7 +3811,7 @@
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,14 +3821,14 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Machine Learning Ops Data Engineer</t>
+          <t>AI/ML Ops and Data Engineer</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Data engineer with Java</t>
+          <t>Machine Learning Ops Data Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, ECS, RDS, Cloud Storage, Scala, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40731666819fe80</t>
+          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE)</t>
+          <t>Data engineer with Java</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, ECS, RDS, Cloud Storage, Scala, ETL</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
+          <t>https://www.indeed.com/viewjob?jk=b40731666819fe80</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
+          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
+          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Optimum Data Modeler - BSS Transformation</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
+          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Remote</t>
+          <t>Optimum Data Modeler - BSS Transformation</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,24 +4066,24 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=985f073bd5ef4e60</t>
+          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Enterprise Data Integration &amp; Migration Senior Associate</t>
+          <t>Sr. Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
@@ -4091,34 +4091,34 @@
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8e3aded50f9da6</t>
+          <t>https://www.indeed.com/viewjob?jk=985f073bd5ef4e60</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Enterprise Data Integration &amp; Migration Senior Associate</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
@@ -4126,34 +4126,34 @@
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1296ebd08a57d7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8e3aded50f9da6</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb71d7121f8589</t>
+          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,7 +4196,7 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
@@ -4206,24 +4206,24 @@
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
+          <t>https://www.indeed.com/viewjob?jk=1296ebd08a57d7ad</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>AI Solutions Architect | US</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,7 +4231,7 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
@@ -4241,67 +4241,67 @@
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb71d7121f8589</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Cronisys IT LLC</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>AI Solutions Architect | US</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,24 +4311,24 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
+          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Workday Everywhere</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Cronisys IT LLC</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
@@ -4336,34 +4336,34 @@
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
@@ -4371,7 +4371,7 @@
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
+          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Software Development Engineer - Workday Everywhere</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,7 +4406,7 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
@@ -4416,14 +4416,14 @@
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
+          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
@@ -4433,7 +4433,7 @@
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
+          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,34 +4476,34 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
+          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Clinical Data Engineer (Application Engineer)</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Oregon Health &amp; Science University</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4511,7 +4511,7 @@
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
+          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Software Engineer III - PA085</t>
+          <t>Clinical Data Engineer (Application Engineer)</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Oregon Health &amp; Science University</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
+          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
+          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
@@ -4626,24 +4626,24 @@
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b234271097cd37b1</t>
+          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Software Engineer III - PA085</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Benson, NC, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc450b1d33691a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
+          <t>Applied Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,34 +4686,34 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
+          <t>https://www.indeed.com/viewjob?jk=b234271097cd37b1</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant level</t>
+          <t>Applied Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Benson, NC, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,17 +4721,17 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc450b1d33691a</t>
         </is>
       </c>
     </row>
@@ -4773,12 +4773,12 @@
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,24 +4801,24 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc906c390155312</t>
+          <t>https://www.indeed.com/viewjob?jk=5777ab28ff195025</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
@@ -4826,34 +4826,34 @@
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57865e75c379265</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,7 +4861,7 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
@@ -4871,7 +4871,7 @@
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f8300de4fecb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc906c390155312</t>
         </is>
       </c>
     </row>
@@ -4888,7 +4888,7 @@
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45adc4c2b25c26f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f57865e75c379265</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Analytics Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,24 +4941,24 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
+          <t>https://www.indeed.com/viewjob?jk=55f8300de4fecb0f</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4966,7 +4966,7 @@
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5777ab28ff195025</t>
+          <t>https://www.indeed.com/viewjob?jk=45adc4c2b25c26f7</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer - Analytics Platform</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Egen Solutions Inc</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Egen Solutions Inc</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
+          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>Kyocera Document Solutions America, Inc.</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>Fairfield, NJ, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,59 +5151,59 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Kyocera Document Solutions America, Inc.</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Fairfield, NJ, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
@@ -5211,17 +5211,17 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
+          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
         </is>
       </c>
     </row>
@@ -5238,7 +5238,7 @@
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
@@ -5256,7 +5256,7 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
+          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
         </is>
       </c>
     </row>
@@ -5273,7 +5273,7 @@
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
@@ -5291,14 +5291,14 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
@@ -5308,7 +5308,7 @@
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5326,14 +5326,14 @@
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,14 +5361,14 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
+          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B142" t="inlineStr">
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,7 +5431,7 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
+          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
         </is>
       </c>
     </row>
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,14 +5466,14 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B145" t="inlineStr">
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
         </is>
       </c>
     </row>
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,7 +5536,7 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
+          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
         </is>
       </c>
     </row>
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
+          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,7 +5606,7 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
         </is>
       </c>
     </row>
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,14 +5676,14 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
+          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B151" t="inlineStr">
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
+          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,7 +5781,7 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
         </is>
       </c>
     </row>
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
+          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,14 +5851,14 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B156" t="inlineStr">
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
         </is>
       </c>
     </row>
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,24 +5921,24 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sr. Associate Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5946,7 +5946,7 @@
       </c>
       <c r="E158" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F158" t="inlineStr">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
+          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Sr. Associate Data Engineer</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>INROADS</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>Bevi</t>
+          <t>INROADS</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Charlestown, MA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, AKS</t>
+          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
+          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>merican Inc</t>
+          <t>Bevi</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Charlestown, MA, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e555efa8f72b69a</t>
+          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>IT Cloud Architect</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>merican Inc</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
+          <t>https://www.indeed.com/viewjob?jk=0e555efa8f72b69a</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Senior Systems &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
+          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>IT Cloud Architect</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
+          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Senior AI Driven Test Automation Architect</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
+          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Senior AI Driven Test Automation Architect</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
+          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>IT Database Engineer</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>Kuehne+Nagel</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Naugatuck, CT, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,7 +6331,7 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
@@ -6341,24 +6341,24 @@
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c73cae1a3da2412</t>
+          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B170" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6366,7 +6366,7 @@
       </c>
       <c r="E170" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F170" t="inlineStr">
@@ -6376,24 +6376,24 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B171" t="inlineStr">
         <is>
-          <t>Sona</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C171" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D171" t="n">
@@ -6401,7 +6401,7 @@
       </c>
       <c r="E171" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F171" t="inlineStr">
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
+          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>Software Engineer – Remote Opportunities</t>
+          <t>IT Database Engineer</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Kuehne+Nagel</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Naugatuck, CT, US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, Git, Python</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a59520fbf843f452</t>
+          <t>https://www.indeed.com/viewjob?jk=9c73cae1a3da2412</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
+          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Senior Java Platform Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Sona</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,7 +6506,7 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
@@ -6516,24 +6516,24 @@
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
+          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Senior Java Platform Engineer</t>
+          <t>Software Engineer – Remote Opportunities</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,7 +6551,7 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=a59520fbf843f452</t>
         </is>
       </c>
     </row>
@@ -6586,24 +6586,24 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
+          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Quality Assurance Specialist</t>
+          <t>Senior Java Platform Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C177" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D177" t="n">
@@ -6611,7 +6611,7 @@
       </c>
       <c r="E177" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F177" t="inlineStr">
@@ -6621,24 +6621,24 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
+          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
         </is>
       </c>
     </row>
     <row r="178">
       <c r="A178" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Senior Java Platform Engineer</t>
         </is>
       </c>
       <c r="B178" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C178" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D178" t="n">
@@ -6646,7 +6646,7 @@
       </c>
       <c r="E178" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F178" t="inlineStr">
@@ -6656,24 +6656,24 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C179" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D179" t="n">
@@ -6681,7 +6681,7 @@
       </c>
       <c r="E179" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
+          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Quality Assurance Specialist</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
+          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>IT Architect - Cloud Platform</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Maximus</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Tysons, VA, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,24 +6761,24 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
+          <t>https://www.indeed.com/viewjob?jk=ef9ea6fc2defb727</t>
         </is>
       </c>
     </row>
     <row r="182">
       <c r="A182" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Associate Developer</t>
         </is>
       </c>
       <c r="B182" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Bealls Inc.</t>
         </is>
       </c>
       <c r="C182" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D182" t="n">
@@ -6786,17 +6786,17 @@
       </c>
       <c r="E182" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F182" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G182" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
+          <t>https://www.indeed.com/viewjob?jk=723d8dc3606ce87f</t>
         </is>
       </c>
     </row>
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
+          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
+          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
+          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,24 +6936,24 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f91c24f3a7633e7</t>
+          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
         </is>
       </c>
     </row>
     <row r="187">
       <c r="A187" t="inlineStr">
         <is>
-          <t>IT Architect - Cloud Platform</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B187" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6961,7 +6961,7 @@
       </c>
       <c r="E187" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F187" t="inlineStr">
@@ -6971,24 +6971,24 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ea6fc2defb727</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
         </is>
       </c>
     </row>
     <row r="188">
       <c r="A188" t="inlineStr">
         <is>
-          <t>Associate Developer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B188" t="inlineStr">
         <is>
-          <t>Bealls Inc.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Bradenton, FL, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -6996,17 +6996,122 @@
       </c>
       <c r="E188" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F188" t="inlineStr">
         <is>
-          <t>2026-06-17</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=723d8dc3606ce87f</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C189" t="inlineStr">
+        <is>
+          <t>New York, NY, US USA</t>
+        </is>
+      </c>
+      <c r="D189" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E189" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G189" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C190" t="inlineStr">
+        <is>
+          <t>Chicago, IL, US USA</t>
+        </is>
+      </c>
+      <c r="D190" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E190" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G190" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C191" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D191" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E191" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=6f91c24f3a7633e7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-24.xlsx
+++ b/results/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G191"/>
+  <dimension ref="A1:G192"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -958,17 +958,17 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
@@ -976,34 +976,34 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,7 +1011,7 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f87cbef2e8672c3</t>
+          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>SD, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0ffa581a9806f2</t>
+          <t>https://www.indeed.com/viewjob?jk=5f87cbef2e8672c3</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>AZ, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a371c6a757e7cc60</t>
+          <t>https://www.indeed.com/viewjob?jk=7d0ffa581a9806f2</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>WY, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c4dc88ae61fe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=a371c6a757e7cc60</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>ME, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,7 +1161,7 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f214eae45940a168</t>
+          <t>https://www.indeed.com/viewjob?jk=b3c4dc88ae61fe0e</t>
         </is>
       </c>
     </row>
@@ -1178,7 +1178,7 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>WA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1196,7 +1196,7 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2687a24e7dad6780</t>
+          <t>https://www.indeed.com/viewjob?jk=f214eae45940a168</t>
         </is>
       </c>
     </row>
@@ -1213,7 +1213,7 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>ND, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1231,7 +1231,7 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba2e28b0686e652</t>
+          <t>https://www.indeed.com/viewjob?jk=2687a24e7dad6780</t>
         </is>
       </c>
     </row>
@@ -1248,7 +1248,7 @@
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>OH, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1266,7 +1266,7 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4555ac252f371341</t>
+          <t>https://www.indeed.com/viewjob?jk=9ba2e28b0686e652</t>
         </is>
       </c>
     </row>
@@ -1283,7 +1283,7 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1301,7 +1301,7 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c21907825eebf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=4555ac252f371341</t>
         </is>
       </c>
     </row>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>KY, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1336,7 +1336,7 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7237946dfe0583b2</t>
+          <t>https://www.indeed.com/viewjob?jk=1c21907825eebf4e</t>
         </is>
       </c>
     </row>
@@ -1353,7 +1353,7 @@
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>LA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1371,7 +1371,7 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801bb2fc81ed28a7</t>
+          <t>https://www.indeed.com/viewjob?jk=7237946dfe0583b2</t>
         </is>
       </c>
     </row>
@@ -1388,7 +1388,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1406,7 +1406,7 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca8ef229b1532c4</t>
+          <t>https://www.indeed.com/viewjob?jk=801bb2fc81ed28a7</t>
         </is>
       </c>
     </row>
@@ -1423,7 +1423,7 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>VA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
@@ -1441,7 +1441,7 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6085a67377b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=0ca8ef229b1532c4</t>
         </is>
       </c>
     </row>
@@ -1458,7 +1458,7 @@
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>FL, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1476,7 +1476,7 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7352e9be8f48d42</t>
+          <t>https://www.indeed.com/viewjob?jk=2a6085a67377b69f</t>
         </is>
       </c>
     </row>
@@ -1493,7 +1493,7 @@
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>MT, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1511,7 +1511,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95dee7b8fef58b1e</t>
+          <t>https://www.indeed.com/viewjob?jk=b7352e9be8f48d42</t>
         </is>
       </c>
     </row>
@@ -1528,7 +1528,7 @@
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>DE, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1546,7 +1546,7 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630ac099235fbd6d</t>
+          <t>https://www.indeed.com/viewjob?jk=95dee7b8fef58b1e</t>
         </is>
       </c>
     </row>
@@ -1563,7 +1563,7 @@
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>TN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1279bb37e0c78ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=630ac099235fbd6d</t>
         </is>
       </c>
     </row>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>SC, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1616,7 +1616,7 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f7accbf789b4d1</t>
+          <t>https://www.indeed.com/viewjob?jk=1279bb37e0c78ee9</t>
         </is>
       </c>
     </row>
@@ -1633,7 +1633,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>VT, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2875a726636cc149</t>
+          <t>https://www.indeed.com/viewjob?jk=02f7accbf789b4d1</t>
         </is>
       </c>
     </row>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1686,7 +1686,7 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44506379a420841e</t>
+          <t>https://www.indeed.com/viewjob?jk=2875a726636cc149</t>
         </is>
       </c>
     </row>
@@ -1703,7 +1703,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>IL, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1721,7 +1721,7 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f29091cd781df40</t>
+          <t>https://www.indeed.com/viewjob?jk=44506379a420841e</t>
         </is>
       </c>
     </row>
@@ -1738,7 +1738,7 @@
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>MS, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
@@ -1756,7 +1756,7 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02feacdf4669a553</t>
+          <t>https://www.indeed.com/viewjob?jk=1f29091cd781df40</t>
         </is>
       </c>
     </row>
@@ -1773,7 +1773,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1791,7 +1791,7 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1b6022ed0acfd4</t>
+          <t>https://www.indeed.com/viewjob?jk=02feacdf4669a553</t>
         </is>
       </c>
     </row>
@@ -1808,7 +1808,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1826,7 +1826,7 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efeae60730c199e0</t>
+          <t>https://www.indeed.com/viewjob?jk=0f1b6022ed0acfd4</t>
         </is>
       </c>
     </row>
@@ -1843,7 +1843,7 @@
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>AR, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1861,7 +1861,7 @@
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2460ff417a265bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=efeae60730c199e0</t>
         </is>
       </c>
     </row>
@@ -1878,7 +1878,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>NE, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1896,7 +1896,7 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1f6380a3c4f83b</t>
+          <t>https://www.indeed.com/viewjob?jk=2460ff417a265bbe</t>
         </is>
       </c>
     </row>
@@ -1913,7 +1913,7 @@
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>KS, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1931,7 +1931,7 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9685333ed2d00ca8</t>
+          <t>https://www.indeed.com/viewjob?jk=6d1f6380a3c4f83b</t>
         </is>
       </c>
     </row>
@@ -1948,7 +1948,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>NM, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21091337a312c8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=9685333ed2d00ca8</t>
         </is>
       </c>
     </row>
@@ -1983,7 +1983,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -2001,7 +2001,7 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f893c944d1eaefab</t>
+          <t>https://www.indeed.com/viewjob?jk=21091337a312c8c7</t>
         </is>
       </c>
     </row>
@@ -2018,7 +2018,7 @@
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
@@ -2036,7 +2036,7 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbf8f230bc8b0c83</t>
+          <t>https://www.indeed.com/viewjob?jk=f893c944d1eaefab</t>
         </is>
       </c>
     </row>
@@ -2053,7 +2053,7 @@
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>NV, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2071,7 +2071,7 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cda9596586f3e32a</t>
+          <t>https://www.indeed.com/viewjob?jk=cbf8f230bc8b0c83</t>
         </is>
       </c>
     </row>
@@ -2088,7 +2088,7 @@
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>WV, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2106,7 +2106,7 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b5df003b7622a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cda9596586f3e32a</t>
         </is>
       </c>
     </row>
@@ -2123,7 +2123,7 @@
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>MD, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2141,7 +2141,7 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8cd995cbc9be6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=20b5df003b7622a9</t>
         </is>
       </c>
     </row>
@@ -2158,7 +2158,7 @@
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>ID, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e4df8e6b664967</t>
+          <t>https://www.indeed.com/viewjob?jk=e8cd995cbc9be6f9</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>CT, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa44bcb3004b69d1</t>
+          <t>https://www.indeed.com/viewjob?jk=c6e4df8e6b664967</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>AL, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,7 +2246,7 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0edbe0ca17f71c</t>
+          <t>https://www.indeed.com/viewjob?jk=fa44bcb3004b69d1</t>
         </is>
       </c>
     </row>
@@ -2263,7 +2263,7 @@
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2281,7 +2281,7 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833ff84fdbb1abd1</t>
+          <t>https://www.indeed.com/viewjob?jk=5c0edbe0ca17f71c</t>
         </is>
       </c>
     </row>
@@ -2298,7 +2298,7 @@
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>CO, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2316,7 +2316,7 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbac48f07a9842df</t>
+          <t>https://www.indeed.com/viewjob?jk=833ff84fdbb1abd1</t>
         </is>
       </c>
     </row>
@@ -2333,7 +2333,7 @@
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>RI, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2351,7 +2351,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb1052d07321fc8</t>
+          <t>https://www.indeed.com/viewjob?jk=fbac48f07a9842df</t>
         </is>
       </c>
     </row>
@@ -2368,7 +2368,7 @@
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>UT, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2386,7 +2386,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2fb4708a4607c9</t>
+          <t>https://www.indeed.com/viewjob?jk=2eb1052d07321fc8</t>
         </is>
       </c>
     </row>
@@ -2403,7 +2403,7 @@
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>IN, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2421,7 +2421,7 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0e9e73889131e2</t>
+          <t>https://www.indeed.com/viewjob?jk=9c2fb4708a4607c9</t>
         </is>
       </c>
     </row>
@@ -2438,7 +2438,7 @@
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>OR, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2456,7 +2456,7 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b93f1cf5124ab</t>
+          <t>https://www.indeed.com/viewjob?jk=ac0e9e73889131e2</t>
         </is>
       </c>
     </row>
@@ -2473,7 +2473,7 @@
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2491,7 +2491,7 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8bd386e42843b</t>
+          <t>https://www.indeed.com/viewjob?jk=176b93f1cf5124ab</t>
         </is>
       </c>
     </row>
@@ -2508,7 +2508,7 @@
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>WI, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2526,7 +2526,7 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e471cdb7ea8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=a9c8bd386e42843b</t>
         </is>
       </c>
     </row>
@@ -2543,7 +2543,7 @@
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>NH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2561,7 +2561,7 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ad11f79e7ed4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=f2e471cdb7ea8fe2</t>
         </is>
       </c>
     </row>
@@ -2578,7 +2578,7 @@
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8935b313a478ee</t>
+          <t>https://www.indeed.com/viewjob?jk=a6ad11f79e7ed4e9</t>
         </is>
       </c>
     </row>
@@ -2613,7 +2613,7 @@
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>MI, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2631,7 +2631,7 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7a4e1799edd25d</t>
+          <t>https://www.indeed.com/viewjob?jk=0a8935b313a478ee</t>
         </is>
       </c>
     </row>
@@ -2648,7 +2648,7 @@
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>OK, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2666,7 +2666,7 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7928d8310dc94518</t>
+          <t>https://www.indeed.com/viewjob?jk=3a7a4e1799edd25d</t>
         </is>
       </c>
     </row>
@@ -2683,7 +2683,7 @@
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>IA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1f237216b5ebbe</t>
+          <t>https://www.indeed.com/viewjob?jk=7928d8310dc94518</t>
         </is>
       </c>
     </row>
@@ -2713,20 +2713,20 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Continuum Media Network Inc</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>TX, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>17.4</v>
+        <v>18.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
+          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
+          <t>https://www.indeed.com/viewjob?jk=bd1f237216b5ebbe</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>Continuum Media Network Inc</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Aurora, CO, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
+          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
+          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
         </is>
       </c>
     </row>
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
+          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,32 +2876,32 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
+          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
+          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,24 +2911,24 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
+          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc1bf7c13d30efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Sr JAVA Full Stack - Lake Mary, FL (Onsite)</t>
+          <t>Senior Backend Software Engineer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>The Washington Post</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, MongoDB, NoSQL, Splunk</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0071b97226cb4875</t>
+          <t>https://www.indeed.com/viewjob?jk=cc1bf7c13d30efa0</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Ad Serving</t>
+          <t>Sr JAVA Full Stack - Lake Mary, FL (Onsite)</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,24 +3016,24 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
+          <t>https://www.indeed.com/viewjob?jk=0071b97226cb4875</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Platform Engineer IV</t>
+          <t>Senior Data Engineer - Ad Serving</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
+          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Data Quality Analyst</t>
+          <t>Platform Engineer IV</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>BBQ Holdings</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,32 +3086,32 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Software Engineerâ€“ Full Stack</t>
+          <t>Data Quality Analyst</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>BBQ Holdings</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>14.6</v>
+        <v>15.3</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,24 +3121,24 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
+          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Senior Software Developer, Automation</t>
+          <t>Software Engineerâ€“ Full Stack</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,24 +3156,24 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
+          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Software Developer, Automation</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Bagel Brands</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Brooklyn Center, MN, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
@@ -3181,34 +3181,34 @@
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
+          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Gen. AI Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Bagel Brands</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Brooklyn Center, MN, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
@@ -3216,42 +3216,42 @@
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
+          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Acquisition</t>
+          <t>Gen. AI Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>People Data Labs</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Fort Worth, TX, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,24 +3261,24 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
+          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Software Engineer, Data Acquisition</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>People Data Labs</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
@@ -3286,7 +3286,7 @@
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,24 +3296,24 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Specialist - Architecture</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
@@ -3321,7 +3321,7 @@
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
+          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
         </is>
       </c>
     </row>
@@ -3348,7 +3348,7 @@
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
@@ -3366,24 +3366,24 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
+          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
@@ -3391,7 +3391,7 @@
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
+          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Senior QA Engineer - Airvoyant</t>
+          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Coral Gables, FL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,59 +3436,59 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
+          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior QA Engineer - Airvoyant</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Coral Gables, FL, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3496,34 +3496,34 @@
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>AWS/EKS Platform Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
@@ -3531,34 +3531,34 @@
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,24 +3576,24 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b26575de63e016</t>
+          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS/EKS Platform Engineer</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
@@ -3601,7 +3601,7 @@
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,24 +3611,24 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d4db52b41a4c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Finance Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>IFS</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
@@ -3636,7 +3636,7 @@
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,24 +3646,24 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
+          <t>https://www.indeed.com/viewjob?jk=c4b26575de63e016</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>FanDuel</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
@@ -3671,7 +3671,7 @@
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,24 +3681,24 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d53fa67d1e5eb8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=22d4db52b41a4c7e</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Senior Finance Data Engineer</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>New York City Department of Citywide Administrative Services</t>
+          <t>IFS</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
@@ -3706,7 +3706,7 @@
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, Azure Cosmos DB, NoSQL, ETL, CI/CD</t>
+          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,24 +3716,24 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8959b284cfe01ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Ragle Inc</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>North Richland Hills, TX, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
@@ -3741,7 +3741,7 @@
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
+          <t>https://www.indeed.com/viewjob?jk=d53fa67d1e5eb8e1</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Software Engineer - 3</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>New York City Department of Citywide Administrative Services</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, Azure Cosmos DB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
+          <t>https://www.indeed.com/viewjob?jk=8959b284cfe01ae8</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>AWS Cloud AI Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,24 +3821,24 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>AI/ML Ops and Data Engineer</t>
+          <t>Software Engineer - 3</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
@@ -3846,7 +3846,7 @@
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,24 +3856,24 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
+          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>Machine Learning Ops Data Engineer</t>
+          <t>AWS Cloud AI Engineer</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,24 +3891,24 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>Data engineer with Java</t>
+          <t>AI/ML Ops and Data Engineer</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
@@ -3916,7 +3916,7 @@
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, ECS, RDS, Cloud Storage, Scala, ETL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,24 +3926,24 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40731666819fe80</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE)</t>
+          <t>Machine Learning Ops Data Engineer</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
@@ -3951,7 +3951,7 @@
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,24 +3961,24 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
+          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data engineer with Java</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Malvern, AR, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
@@ -3986,7 +3986,7 @@
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Glue, Lambda, Redshift, API Gateway, ECS, RDS, Cloud Storage, Scala, ETL</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,24 +3996,24 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
+          <t>https://www.indeed.com/viewjob?jk=b40731666819fe80</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
@@ -4021,7 +4021,7 @@
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,24 +4031,24 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
+          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Optimum Data Modeler - BSS Transformation</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
+          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Remote</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,59 +4101,59 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=985f073bd5ef4e60</t>
+          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Enterprise Data Integration &amp; Migration Senior Associate</t>
+          <t>Optimum Data Modeler - BSS Transformation</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>11.8</v>
+        <v>12.5</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, Snowflake Schema, ETL</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8e3aded50f9da6</t>
+          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Data Engineer - Remote</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
@@ -4161,34 +4161,34 @@
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
+          <t>https://www.indeed.com/viewjob?jk=985f073bd5ef4e60</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Enterprise Data Integration &amp; Migration Senior Associate</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>RSM</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
@@ -4196,34 +4196,34 @@
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, Snowflake Schema, ETL</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-21</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1296ebd08a57d7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=ec8e3aded50f9da6</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
@@ -4231,34 +4231,34 @@
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb71d7121f8589</t>
+          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Downers Grove, IL, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
@@ -4266,7 +4266,7 @@
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,24 +4276,24 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
+          <t>https://www.indeed.com/viewjob?jk=1296ebd08a57d7ad</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>AI Solutions Architect | US</t>
+          <t>SQL Server DBA</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>Kemper</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
@@ -4301,7 +4301,7 @@
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
+          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,67 +4311,67 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
+          <t>https://www.indeed.com/viewjob?jk=95bb71d7121f8589</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Cronisys IT LLC</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>AI Solutions Architect | US</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.1</v>
+        <v>11.8</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
@@ -4381,24 +4381,24 @@
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
+          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Workday Everywhere</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Cronisys IT LLC</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
@@ -4406,34 +4406,34 @@
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D115" t="n">
@@ -4441,7 +4441,7 @@
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
@@ -4451,24 +4451,24 @@
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
+          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Software Development Engineer - Workday Everywhere</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
@@ -4476,7 +4476,7 @@
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,14 +4486,14 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
+          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
@@ -4503,7 +4503,7 @@
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
@@ -4521,24 +4521,24 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
+          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
@@ -4546,34 +4546,34 @@
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
+          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Clinical Data Engineer (Application Engineer)</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Oregon Health &amp; Science University</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
@@ -4581,7 +4581,7 @@
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,24 +4591,24 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
+          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
@@ -4616,34 +4616,34 @@
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Software Engineer III - PA085</t>
+          <t>Clinical Data Engineer (Application Engineer)</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Oregon Health &amp; Science University</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
+          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,24 +4661,24 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
+          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
@@ -4686,7 +4686,7 @@
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,24 +4696,24 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b234271097cd37b1</t>
+          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Software Engineer III - PA085</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Benson, NC, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
@@ -4721,7 +4721,7 @@
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,24 +4731,24 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc450b1d33691a</t>
+          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Applied Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
@@ -4756,7 +4756,7 @@
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,24 +4766,24 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=b234271097cd37b1</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
+          <t>Applied Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Benson, NC, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
@@ -4791,7 +4791,7 @@
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,7 +4801,7 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5777ab28ff195025</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc450b1d33691a</t>
         </is>
       </c>
     </row>
@@ -4843,17 +4843,17 @@
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>SW Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
@@ -4861,34 +4861,34 @@
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, Docker</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc906c390155312</t>
+          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
@@ -4896,7 +4896,7 @@
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,24 +4906,24 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57865e75c379265</t>
+          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Senior Specialist - Architecture</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>LTM Limited</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
@@ -4931,7 +4931,7 @@
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, Docker</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,7 +4941,7 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f8300de4fecb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=4bc906c390155312</t>
         </is>
       </c>
     </row>
@@ -4958,7 +4958,7 @@
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Rockville, MD, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
@@ -4976,24 +4976,24 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45adc4c2b25c26f7</t>
+          <t>https://www.indeed.com/viewjob?jk=f57865e75c379265</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Analytics Platform</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>McLean, VA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
@@ -5001,7 +5001,7 @@
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,24 +5011,24 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
+          <t>https://www.indeed.com/viewjob?jk=55f8300de4fecb0f</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>FINRA</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
@@ -5036,7 +5036,7 @@
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,24 +5046,24 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=45adc4c2b25c26f7</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Senior Software Engineer - Analytics Platform</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Bloomberg</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, SonarQube</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,24 +5081,24 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
+          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
+          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Egen Solutions Inc</t>
+          <t>Frontline Education</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
@@ -5106,7 +5106,7 @@
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
@@ -5116,24 +5116,24 @@
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
+          <t>https://www.indeed.com/viewjob?jk=5777ab28ff195025</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D135" t="n">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
@@ -5151,24 +5151,24 @@
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B136" t="inlineStr">
         <is>
-          <t>Kyocera Document Solutions America, Inc.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C136" t="inlineStr">
         <is>
-          <t>Fairfield, NJ, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D136" t="n">
@@ -5176,7 +5176,7 @@
       </c>
       <c r="E136" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F136" t="inlineStr">
@@ -5186,67 +5186,67 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
         </is>
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Egen Solutions Inc</t>
         </is>
       </c>
       <c r="C137" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D137" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
+          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C138" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D138" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F138" t="inlineStr">
@@ -5256,32 +5256,32 @@
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
+          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Kyocera Document Solutions America, Inc.</t>
         </is>
       </c>
       <c r="C139" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Fairfield, NJ, US USA</t>
         </is>
       </c>
       <c r="D139" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F139" t="inlineStr">
@@ -5291,24 +5291,24 @@
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C140" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D140" t="n">
@@ -5316,24 +5316,24 @@
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
+          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B141" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D141" t="n">
@@ -5361,7 +5361,7 @@
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
+          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
         </is>
       </c>
     </row>
@@ -5378,7 +5378,7 @@
       </c>
       <c r="C142" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D142" t="n">
@@ -5396,14 +5396,14 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B143" t="inlineStr">
@@ -5413,7 +5413,7 @@
       </c>
       <c r="C143" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D143" t="n">
@@ -5431,14 +5431,14 @@
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
+          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B144" t="inlineStr">
@@ -5448,7 +5448,7 @@
       </c>
       <c r="C144" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D144" t="n">
@@ -5466,7 +5466,7 @@
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
+          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
         </is>
       </c>
     </row>
@@ -5483,7 +5483,7 @@
       </c>
       <c r="C145" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D145" t="n">
@@ -5501,14 +5501,14 @@
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
+          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B146" t="inlineStr">
@@ -5518,7 +5518,7 @@
       </c>
       <c r="C146" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D146" t="n">
@@ -5536,14 +5536,14 @@
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
+          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B147" t="inlineStr">
@@ -5553,7 +5553,7 @@
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D147" t="n">
@@ -5571,14 +5571,14 @@
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B148" t="inlineStr">
@@ -5588,7 +5588,7 @@
       </c>
       <c r="C148" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D148" t="n">
@@ -5606,14 +5606,14 @@
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B149" t="inlineStr">
@@ -5623,7 +5623,7 @@
       </c>
       <c r="C149" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D149" t="n">
@@ -5641,14 +5641,14 @@
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
+          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B150" t="inlineStr">
@@ -5658,7 +5658,7 @@
       </c>
       <c r="C150" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D150" t="n">
@@ -5676,7 +5676,7 @@
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
+          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
         </is>
       </c>
     </row>
@@ -5693,7 +5693,7 @@
       </c>
       <c r="C151" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D151" t="n">
@@ -5711,7 +5711,7 @@
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
         </is>
       </c>
     </row>
@@ -5728,7 +5728,7 @@
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D152" t="n">
@@ -5746,7 +5746,7 @@
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
         </is>
       </c>
     </row>
@@ -5763,7 +5763,7 @@
       </c>
       <c r="C153" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D153" t="n">
@@ -5781,14 +5781,14 @@
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
+          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B154" t="inlineStr">
@@ -5798,7 +5798,7 @@
       </c>
       <c r="C154" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D154" t="n">
@@ -5816,7 +5816,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
         </is>
       </c>
     </row>
@@ -5833,7 +5833,7 @@
       </c>
       <c r="C155" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D155" t="n">
@@ -5851,7 +5851,7 @@
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
+          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
         </is>
       </c>
     </row>
@@ -5868,7 +5868,7 @@
       </c>
       <c r="C156" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D156" t="n">
@@ -5886,14 +5886,14 @@
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
+          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B157" t="inlineStr">
@@ -5903,7 +5903,7 @@
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D157" t="n">
@@ -5921,14 +5921,14 @@
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
+          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B158" t="inlineStr">
@@ -5938,7 +5938,7 @@
       </c>
       <c r="C158" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D158" t="n">
@@ -5956,24 +5956,24 @@
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>Sr. Associate Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B159" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C159" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D159" t="n">
@@ -5981,7 +5981,7 @@
       </c>
       <c r="E159" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F159" t="inlineStr">
@@ -5991,24 +5991,24 @@
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
+          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>AI Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B160" t="inlineStr">
         <is>
-          <t>Syracuse University</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C160" t="inlineStr">
         <is>
-          <t>Syracuse, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D160" t="n">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="E160" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F160" t="inlineStr">
@@ -6026,24 +6026,24 @@
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B161" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C161" t="inlineStr">
         <is>
-          <t>Eden Prairie, MN, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D161" t="n">
@@ -6051,7 +6051,7 @@
       </c>
       <c r="E161" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F161" t="inlineStr">
@@ -6061,24 +6061,24 @@
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
+          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
         <is>
-          <t>Data Engineer I</t>
+          <t>Sr. Associate Data Engineer</t>
         </is>
       </c>
       <c r="B162" t="inlineStr">
         <is>
-          <t>INROADS</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C162" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D162" t="n">
@@ -6086,7 +6086,7 @@
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F162" t="inlineStr">
@@ -6096,24 +6096,24 @@
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
+          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="inlineStr">
         <is>
-          <t>Senior Data Platform Engineer</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B163" t="inlineStr">
         <is>
-          <t>Bevi</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C163" t="inlineStr">
         <is>
-          <t>Charlestown, MA, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D163" t="n">
@@ -6121,7 +6121,7 @@
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, AKS</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F163" t="inlineStr">
@@ -6131,24 +6131,24 @@
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="inlineStr">
         <is>
-          <t>Snowflake Architect</t>
+          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
         </is>
       </c>
       <c r="B164" t="inlineStr">
         <is>
-          <t>merican Inc</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C164" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D164" t="n">
@@ -6156,7 +6156,7 @@
       </c>
       <c r="E164" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F164" t="inlineStr">
@@ -6166,24 +6166,24 @@
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0e555efa8f72b69a</t>
+          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Backend Engineer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B165" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>INROADS</t>
         </is>
       </c>
       <c r="C165" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D165" t="n">
@@ -6191,34 +6191,34 @@
       </c>
       <c r="E165" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="inlineStr">
         <is>
-          <t>IT Cloud Architect</t>
+          <t>Senior Data Platform Engineer</t>
         </is>
       </c>
       <c r="B166" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>Bevi</t>
         </is>
       </c>
       <c r="C166" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Charlestown, MA, US USA</t>
         </is>
       </c>
       <c r="D166" t="n">
@@ -6226,7 +6226,7 @@
       </c>
       <c r="E166" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, AKS</t>
         </is>
       </c>
       <c r="F166" t="inlineStr">
@@ -6236,24 +6236,24 @@
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
+          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="inlineStr">
         <is>
-          <t>Senior AI Driven Test Automation Architect</t>
+          <t>Snowflake Architect</t>
         </is>
       </c>
       <c r="B167" t="inlineStr">
         <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
+          <t>merican Inc</t>
         </is>
       </c>
       <c r="C167" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D167" t="n">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="E167" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
+          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
         </is>
       </c>
       <c r="F167" t="inlineStr">
@@ -6271,24 +6271,24 @@
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
+          <t>https://www.indeed.com/viewjob?jk=0e555efa8f72b69a</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>IT Cloud Architect</t>
         </is>
       </c>
       <c r="B168" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C168" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D168" t="n">
@@ -6296,7 +6296,7 @@
       </c>
       <c r="E168" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F168" t="inlineStr">
@@ -6306,24 +6306,24 @@
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
+          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Senior Systems &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B169" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C169" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D169" t="n">
@@ -6331,17 +6331,17 @@
       </c>
       <c r="E169" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
+          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
         </is>
       </c>
     </row>
@@ -6358,7 +6358,7 @@
       </c>
       <c r="C170" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D170" t="n">
@@ -6376,7 +6376,7 @@
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
+          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
         </is>
       </c>
     </row>
@@ -6411,24 +6411,24 @@
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="inlineStr">
         <is>
-          <t>IT Database Engineer</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B172" t="inlineStr">
         <is>
-          <t>Kuehne+Nagel</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C172" t="inlineStr">
         <is>
-          <t>Naugatuck, CT, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D172" t="n">
@@ -6436,7 +6436,7 @@
       </c>
       <c r="E172" t="inlineStr">
         <is>
-          <t>AWS, RDS, Scala, SQL Server, PostgreSQL, MySQL, CI/CD, Terraform, Git, Python</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F172" t="inlineStr">
@@ -6446,24 +6446,24 @@
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c73cae1a3da2412</t>
+          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Senior AI Driven Test Automation Architect</t>
         </is>
       </c>
       <c r="B173" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C173" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D173" t="n">
@@ -6471,34 +6471,34 @@
       </c>
       <c r="E173" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
         </is>
       </c>
     </row>
     <row r="174">
       <c r="A174" t="inlineStr">
         <is>
-          <t>Software Engineer</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B174" t="inlineStr">
         <is>
-          <t>Sona</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C174" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D174" t="n">
@@ -6506,34 +6506,34 @@
       </c>
       <c r="E174" t="inlineStr">
         <is>
-          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F174" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G174" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
+          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
         </is>
       </c>
     </row>
     <row r="175">
       <c r="A175" t="inlineStr">
         <is>
-          <t>Software Engineer – Remote Opportunities</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B175" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Sona</t>
         </is>
       </c>
       <c r="C175" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D175" t="n">
@@ -6541,7 +6541,7 @@
       </c>
       <c r="E175" t="inlineStr">
         <is>
-          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
+          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F175" t="inlineStr">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="G175" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a59520fbf843f452</t>
+          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
         </is>
       </c>
     </row>
     <row r="176">
       <c r="A176" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Software Engineer – Remote Opportunities</t>
         </is>
       </c>
       <c r="B176" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C176" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D176" t="n">
@@ -6576,7 +6576,7 @@
       </c>
       <c r="E176" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
+          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F176" t="inlineStr">
@@ -6586,14 +6586,14 @@
       </c>
       <c r="G176" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
+          <t>https://www.indeed.com/viewjob?jk=a59520fbf843f452</t>
         </is>
       </c>
     </row>
     <row r="177">
       <c r="A177" t="inlineStr">
         <is>
-          <t>Senior Java Platform Engineer</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B177" t="inlineStr">
@@ -6621,7 +6621,7 @@
       </c>
       <c r="G177" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
+          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
         </is>
       </c>
     </row>
@@ -6656,14 +6656,14 @@
       </c>
       <c r="G178" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
+          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
         </is>
       </c>
     </row>
     <row r="179">
       <c r="A179" t="inlineStr">
         <is>
-          <t>Java Platform Engineer</t>
+          <t>Senior Java Platform Engineer</t>
         </is>
       </c>
       <c r="B179" t="inlineStr">
@@ -6691,24 +6691,24 @@
       </c>
       <c r="G179" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
+          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
         </is>
       </c>
     </row>
     <row r="180">
       <c r="A180" t="inlineStr">
         <is>
-          <t>Quality Assurance Specialist</t>
+          <t>Java Platform Engineer</t>
         </is>
       </c>
       <c r="B180" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C180" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D180" t="n">
@@ -6716,7 +6716,7 @@
       </c>
       <c r="E180" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
         </is>
       </c>
       <c r="F180" t="inlineStr">
@@ -6726,24 +6726,24 @@
       </c>
       <c r="G180" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
+          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
         </is>
       </c>
     </row>
     <row r="181">
       <c r="A181" t="inlineStr">
         <is>
-          <t>IT Architect - Cloud Platform</t>
+          <t>Quality Assurance Specialist</t>
         </is>
       </c>
       <c r="B181" t="inlineStr">
         <is>
-          <t>Maximus</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C181" t="inlineStr">
         <is>
-          <t>Tysons, VA, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D181" t="n">
@@ -6751,7 +6751,7 @@
       </c>
       <c r="E181" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Scala, ETL, Talend, CI/CD, Jenkins, Kubernetes, Jenkins</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F181" t="inlineStr">
@@ -6761,7 +6761,7 @@
       </c>
       <c r="G181" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ef9ea6fc2defb727</t>
+          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
         </is>
       </c>
     </row>
@@ -6803,7 +6803,7 @@
     <row r="183">
       <c r="A183" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B183" t="inlineStr">
@@ -6813,7 +6813,7 @@
       </c>
       <c r="C183" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D183" t="n">
@@ -6831,7 +6831,7 @@
       </c>
       <c r="G183" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
+          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
         </is>
       </c>
     </row>
@@ -6848,7 +6848,7 @@
       </c>
       <c r="C184" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D184" t="n">
@@ -6866,7 +6866,7 @@
       </c>
       <c r="G184" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
+          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
         </is>
       </c>
     </row>
@@ -6883,7 +6883,7 @@
       </c>
       <c r="C185" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D185" t="n">
@@ -6901,7 +6901,7 @@
       </c>
       <c r="G185" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
+          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
         </is>
       </c>
     </row>
@@ -6918,7 +6918,7 @@
       </c>
       <c r="C186" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D186" t="n">
@@ -6936,7 +6936,7 @@
       </c>
       <c r="G186" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
+          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
         </is>
       </c>
     </row>
@@ -6953,7 +6953,7 @@
       </c>
       <c r="C187" t="inlineStr">
         <is>
-          <t>Charlotte, NC, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D187" t="n">
@@ -6971,7 +6971,7 @@
       </c>
       <c r="G187" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
+          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
         </is>
       </c>
     </row>
@@ -6988,7 +6988,7 @@
       </c>
       <c r="C188" t="inlineStr">
         <is>
-          <t>Central, LA, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D188" t="n">
@@ -7006,7 +7006,7 @@
       </c>
       <c r="G188" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
         </is>
       </c>
     </row>
@@ -7023,7 +7023,7 @@
       </c>
       <c r="C189" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D189" t="n">
@@ -7041,7 +7041,7 @@
       </c>
       <c r="G189" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
         </is>
       </c>
     </row>
@@ -7058,7 +7058,7 @@
       </c>
       <c r="C190" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D190" t="n">
@@ -7076,7 +7076,7 @@
       </c>
       <c r="G190" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
+          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
         </is>
       </c>
     </row>
@@ -7093,7 +7093,7 @@
       </c>
       <c r="C191" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D191" t="n">
@@ -7110,6 +7110,41 @@
         </is>
       </c>
       <c r="G191" t="inlineStr">
+        <is>
+          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>Databricks</t>
+        </is>
+      </c>
+      <c r="C192" t="inlineStr">
+        <is>
+          <t>Philadelphia, PA, US USA</t>
+        </is>
+      </c>
+      <c r="D192" t="n">
+        <v>10.4</v>
+      </c>
+      <c r="E192" t="inlineStr">
+        <is>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+        </is>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>2026-07-23</t>
+        </is>
+      </c>
+      <c r="G192" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6f91c24f3a7633e7</t>
         </is>

--- a/results/job_matches_2026-07-24.xlsx
+++ b/results/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G192"/>
+  <dimension ref="A1:G134"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III-Databricks</t>
+          <t>Hadoop Solutions Developer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.8</v>
+        <v>20.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4788de97836b6e30</t>
+          <t>https://www.indeed.com/viewjob?jk=5b43cb1da9bd5e66</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
+          <t>Software Engineer III-Databricks</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.1</v>
+        <v>18.8</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
+          <t>https://www.indeed.com/viewjob?jk=4788de97836b6e30</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,24 +1011,24 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
+          <t>https://www.indeed.com/viewjob?jk=6bea0599e34ce74e</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>SD, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1046,34 +1046,34 @@
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5f87cbef2e8672c3</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>AZ, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1081,7 +1081,7 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,24 +1091,24 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7d0ffa581a9806f2</t>
+          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Solutions Architect</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>WY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1116,17 +1116,17 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a371c6a757e7cc60</t>
+          <t>https://www.indeed.com/viewjob?jk=3ca7ef41ca26d3ec</t>
         </is>
       </c>
     </row>
@@ -1138,20 +1138,20 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Continuum Media Network Inc</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>ME, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b3c4dc88ae61fe0e</t>
+          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>WA, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f214eae45940a168</t>
+          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>ND, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2687a24e7dad6780</t>
+          <t>https://www.indeed.com/viewjob?jk=b019316b66042eb5</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>OH, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9ba2e28b0686e652</t>
+          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,32 +1301,32 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4555ac252f371341</t>
+          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>KY, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>18.1</v>
+        <v>16.7</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,32 +1336,32 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c21907825eebf4e</t>
+          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>LA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>18.1</v>
+        <v>16</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,32 +1371,32 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7237946dfe0583b2</t>
+          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer - Ad Serving</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=801bb2fc81ed28a7</t>
+          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Platform Engineer IV</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>VA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,32 +1441,32 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0ca8ef229b1532c4</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Quality Analyst</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BBQ Holdings</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>FL, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>18.1</v>
+        <v>15.3</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
@@ -1476,32 +1476,32 @@
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2a6085a67377b69f</t>
+          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineerâ€“ Full Stack</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cisco</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>MT, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,32 +1511,32 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b7352e9be8f48d42</t>
+          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Developer, Automation</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>DE, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,67 +1546,67 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95dee7b8fef58b1e</t>
+          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Bagel Brands</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>TN, US USA</t>
+          <t>Brooklyn Center, MN, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>18.1</v>
+        <v>14.6</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=630ac099235fbd6d</t>
+          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer, Data Acquisition</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>People Data Labs</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>SC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>18.1</v>
+        <v>13.9</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,102 +1616,102 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1279bb37e0c78ee9</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>VT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>18.1</v>
+        <v>13.9</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02f7accbf789b4d1</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Cloud Solutions Engineer – Azure</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>18.1</v>
+        <v>13.9</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2875a726636cc149</t>
+          <t>https://www.indeed.com/viewjob?jk=f56342ea02089099</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>IL, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>18.1</v>
+        <v>13.9</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=44506379a420841e</t>
+          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior QA Engineer - Airvoyant</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>MS, US USA</t>
+          <t>Coral Gables, FL, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>18.1</v>
+        <v>13.9</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,137 +1756,137 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1f29091cd781df40</t>
+          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>NC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02feacdf4669a553</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0f1b6022ed0acfd4</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>AR, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=efeae60730c199e0</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>NE, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
@@ -1896,32 +1896,32 @@
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2460ff417a265bbe</t>
+          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS/EKS Platform Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>KS, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d1f6380a3c4f83b</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>OCI Solutions Architect</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>NM, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9685333ed2d00ca8</t>
+          <t>https://www.indeed.com/viewjob?jk=1e360996f49b9bba</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Application Developer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>New York City Department of Citywide Administrative Services</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>MN, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, Azure Cosmos DB, NoSQL, ETL, CI/CD</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,32 +2001,32 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=21091337a312c8c7</t>
+          <t>https://www.indeed.com/viewjob?jk=8959b284cfe01ae8</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>MA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f893c944d1eaefab</t>
+          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer - 3</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>NV, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,32 +2071,32 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cbf8f230bc8b0c83</t>
+          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AWS Cloud AI Engineer</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>WV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
@@ -2106,32 +2106,32 @@
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cda9596586f3e32a</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI/ML Ops and Data Engineer</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MD, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,32 +2141,32 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20b5df003b7622a9</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Machine Learning Ops Data Engineer</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>ID, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,172 +2176,172 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e8cd995cbc9be6f9</t>
+          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise ServiceNow Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>CT, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c6e4df8e6b664967</t>
+          <t>https://www.indeed.com/viewjob?jk=dc18d561962fcd21</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Enterprise Data Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fa44bcb3004b69d1</t>
+          <t>https://www.indeed.com/viewjob?jk=20d65d994c35df77</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5c0edbe0ca17f71c</t>
+          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>CO, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=833ff84fdbb1abd1</t>
+          <t>https://www.indeed.com/viewjob?jk=e00458dd00ce6b98</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>RI, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,32 +2351,32 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fbac48f07a9842df</t>
+          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>UT, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,32 +2386,32 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2eb1052d07321fc8</t>
+          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>IN, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
@@ -2421,32 +2421,32 @@
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9c2fb4708a4607c9</t>
+          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Optimum Data Modeler - BSS Transformation</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>OR, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>18.1</v>
+        <v>12.5</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,67 +2456,67 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ac0e9e73889131e2</t>
+          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Python Software Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>18.1</v>
+        <v>11.8</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=176b93f1cf5124ab</t>
+          <t>https://www.indeed.com/viewjob?jk=6d70d40d60ab2d22</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>AI Solutions Architect | US</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>WI, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>18.1</v>
+        <v>11.8</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,67 +2526,67 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9c8bd386e42843b</t>
+          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>NH, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>18.1</v>
+        <v>11.8</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f2e471cdb7ea8fe2</t>
+          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>NJ, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>18.1</v>
+        <v>11.8</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
@@ -2596,7 +2596,7 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a6ad11f79e7ed4e9</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
         </is>
       </c>
     </row>
@@ -2608,55 +2608,55 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Cronisys IT LLC</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>MI, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>18.1</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0a8935b313a478ee</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>OK, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
-        <v>18.1</v>
+        <v>11.1</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,32 +2666,32 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a7a4e1799edd25d</t>
+          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Software Development Engineer - Workday Everywhere</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>IA, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
-        <v>18.1</v>
+        <v>11.1</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,32 +2701,32 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7928d8310dc94518</t>
+          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>TX, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>18.1</v>
+        <v>11.1</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, SNS, RDS, Azure, Synapse Analytics, Databricks, BigQuery, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,32 +2736,32 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bd1f237216b5ebbe</t>
+          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Continuum Media Network Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>17.4</v>
+        <v>11.1</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,32 +2771,32 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
+          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Aurora, CO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>17.4</v>
+        <v>11.1</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,137 +2806,137 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
+          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
+          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>16.7</v>
+        <v>11.1</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
+          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
+          <t>Clinical Data Engineer (Application Engineer)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Oregon Health &amp; Science University</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,32 +2946,32 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
+          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Backend Software Engineer</t>
+          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>The Washington Post</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, ECS, RDS, Scala, MySQL, MongoDB, NoSQL, Splunk</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,32 +2981,32 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cc1bf7c13d30efa0</t>
+          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Sr JAVA Full Stack - Lake Mary, FL (Onsite)</t>
+          <t>Software Engineer III - PA085</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>16</v>
+        <v>11.1</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, Oracle, SQL Server, PostgreSQL</t>
+          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,32 +3016,32 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=0071b97226cb4875</t>
+          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Ad Serving</t>
+          <t>Applied Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Durham, NC, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,32 +3051,32 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
+          <t>https://www.indeed.com/viewjob?jk=b234271097cd37b1</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Platform Engineer IV</t>
+          <t>Applied Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Vulcan Elements</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Benson, NC, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,102 +3086,102 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
+          <t>https://www.indeed.com/viewjob?jk=16fc450b1d33691a</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Data Quality Analyst</t>
+          <t>Test Automation Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BBQ Holdings</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
-        <v>15.3</v>
+        <v>11.1</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
+          <t>https://www.indeed.com/viewjob?jk=f73b61f08926eb79</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Software Engineerâ€“ Full Stack</t>
+          <t>SW Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
+          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Software Developer, Automation</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
+          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Bagel Brands</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Brooklyn Center, MN, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Gen. AI Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Fort Worth, TX, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>14.6</v>
+        <v>11.1</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, Spark, Scala, Kafka, Snowflake, CI/CD, Jenkins</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=29fda9131139079e</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Acquisition</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>People Data Labs</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Specialist - Architecture</t>
+          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Egen Solutions Inc</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>RDS, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, PySpark, Scala, Kafka</t>
+          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,32 +3331,32 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=760cf46880d813e3</t>
+          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior DevOps Engineer</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>accrete</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
@@ -3366,32 +3366,32 @@
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0124c68aa711e39</t>
+          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Kyocera Document Solutions America, Inc.</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Fairfield, NJ, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>13.9</v>
+        <v>11.1</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,67 +3401,67 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7403c7f190048d2a</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
+          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Senior QA Engineer - Airvoyant</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Coral Gables, FL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
-        <v>13.9</v>
+        <v>10.4</v>
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,102 +3471,102 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
+          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E88" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D89" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E89" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>CA, US USA</t>
         </is>
       </c>
       <c r="D90" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E90" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F90" t="inlineStr">
@@ -3576,32 +3576,32 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>AWS/EKS Platform Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C91" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D91" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E91" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F91" t="inlineStr">
@@ -3611,32 +3611,32 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
         </is>
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D92" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E92" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F92" t="inlineStr">
@@ -3646,32 +3646,32 @@
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4b26575de63e016</t>
+          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B93" t="inlineStr">
         <is>
-          <t>FanDuel</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C93" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D93" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E93" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, Kafka, Data Modeling, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F93" t="inlineStr">
@@ -3681,32 +3681,32 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22d4db52b41a4c7e</t>
+          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="inlineStr">
         <is>
-          <t>Senior Finance Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>IFS</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D94" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E94" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Spark, PySpark, Scala, Snowflake, Dimensional Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F94" t="inlineStr">
@@ -3716,32 +3716,32 @@
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=470c48d671a5aed8</t>
+          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>Ragle Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
         <is>
-          <t>North Richland Hills, TX, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D95" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E95" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Scala, SQL Server, Data Modeling, Star Schema, Dimension Tables, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F95" t="inlineStr">
@@ -3751,32 +3751,32 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d53fa67d1e5eb8e1</t>
+          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>New York City Department of Citywide Administrative Services</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C96" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D96" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E96" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, Azure Cosmos DB, NoSQL, ETL, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F96" t="inlineStr">
@@ -3786,32 +3786,32 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8959b284cfe01ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D97" t="n">
-        <v>13.2</v>
+        <v>10.4</v>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
@@ -3821,32 +3821,32 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
+          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t>Software Engineer - 3</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C98" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D98" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E98" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F98" t="inlineStr">
@@ -3856,32 +3856,32 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t>AWS Cloud AI Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C99" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D99" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E99" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F99" t="inlineStr">
@@ -3891,32 +3891,32 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>AI/ML Ops and Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C100" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D100" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E100" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F100" t="inlineStr">
@@ -3926,32 +3926,32 @@
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
+          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>Machine Learning Ops Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C101" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D101" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E101" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F101" t="inlineStr">
@@ -3961,32 +3961,32 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>Data engineer with Java</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>Malvern, AR, US USA</t>
+          <t>Mountain View, CA, US USA</t>
         </is>
       </c>
       <c r="D102" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Redshift, API Gateway, ECS, RDS, Cloud Storage, Scala, ETL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
@@ -3996,32 +3996,32 @@
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b40731666819fe80</t>
+          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE)</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C103" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D103" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E103" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F103" t="inlineStr">
@@ -4031,32 +4031,32 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
+          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C104" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D104" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F104" t="inlineStr">
@@ -4066,32 +4066,32 @@
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
+          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
         </is>
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C105" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>San Francisco, CA, US USA</t>
         </is>
       </c>
       <c r="D105" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F105" t="inlineStr">
@@ -4101,32 +4101,32 @@
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
+          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>Optimum Data Modeler - BSS Transformation</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C106" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D106" t="n">
-        <v>12.5</v>
+        <v>10.4</v>
       </c>
       <c r="E106" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F106" t="inlineStr">
@@ -4136,32 +4136,32 @@
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
+          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>Sr. Data Engineer - Remote</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
         </is>
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>Optum</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>Little Rock, AR, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D107" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Dataflow, Scala, Snowflake, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
@@ -4171,102 +4171,102 @@
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=985f073bd5ef4e60</t>
+          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>Enterprise Data Integration &amp; Migration Senior Associate</t>
+          <t>Container Platform Engineer</t>
         </is>
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>RSM</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C108" t="inlineStr">
         <is>
-          <t>Philadelphia, PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D108" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E108" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, GCP, Scala, Snowflake, Oracle, Snowflake Schema, ETL</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
         </is>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>2026-07-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ec8e3aded50f9da6</t>
+          <t>https://www.indeed.com/viewjob?jk=5b12ac3bb4713b71</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Sr. Associate Data Engineer</t>
         </is>
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C109" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D109" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E109" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
+          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>AI Data Engineer</t>
         </is>
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Syracuse University</t>
         </is>
       </c>
       <c r="C110" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Syracuse, NY, US USA</t>
         </is>
       </c>
       <c r="D110" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E110" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
         </is>
       </c>
       <c r="F110" t="inlineStr">
@@ -4276,32 +4276,32 @@
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1296ebd08a57d7ad</t>
+          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>SQL Server DBA</t>
+          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
         </is>
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Optum</t>
         </is>
       </c>
       <c r="C111" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Eden Prairie, MN, US USA</t>
         </is>
       </c>
       <c r="D111" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E111" t="inlineStr">
         <is>
-          <t>AWS, S3, IAM, RDS, Azure, Scala, SQL Server, Data Modeling, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
         </is>
       </c>
       <c r="F111" t="inlineStr">
@@ -4311,32 +4311,32 @@
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=95bb71d7121f8589</t>
+          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Data Engineer I</t>
         </is>
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>INROADS</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D112" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
@@ -4346,89 +4346,89 @@
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
+          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>AI Solutions Architect | US</t>
+          <t>Senior Systems &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C113" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D113" t="n">
-        <v>11.8</v>
+        <v>10.4</v>
       </c>
       <c r="E113" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
+          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>IT Cloud Architect</t>
         </is>
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>Cronisys IT LLC</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C114" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D114" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E114" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C115" t="inlineStr">
@@ -4437,46 +4437,46 @@
         </is>
       </c>
       <c r="D115" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E115" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
+          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Workday Everywhere</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C116" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D116" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E116" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F116" t="inlineStr">
@@ -4486,32 +4486,32 @@
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
+          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C117" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D117" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E117" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F117" t="inlineStr">
@@ -4521,32 +4521,32 @@
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D118" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
@@ -4556,32 +4556,32 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
+          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior AI Driven Test Automation Architect</t>
         </is>
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C119" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D119" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E119" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F119" t="inlineStr">
@@ -4591,67 +4591,67 @@
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
+          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C120" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D120" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E120" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
+          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>Clinical Data Engineer (Application Engineer)</t>
+          <t>Quality Assurance Specialist</t>
         </is>
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>Oregon Health &amp; Science University</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C121" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D121" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E121" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F121" t="inlineStr">
@@ -4661,32 +4661,32 @@
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
+          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B122" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C122" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D122" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E122" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F122" t="inlineStr">
@@ -4696,32 +4696,32 @@
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>Software Engineer III - PA085</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B123" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C123" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D123" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E123" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F123" t="inlineStr">
@@ -4731,32 +4731,32 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
+          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D124" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
@@ -4766,32 +4766,32 @@
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b234271097cd37b1</t>
+          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B125" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C125" t="inlineStr">
         <is>
-          <t>Benson, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D125" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E125" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F125" t="inlineStr">
@@ -4801,102 +4801,102 @@
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc450b1d33691a</t>
+          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B126" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C126" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D126" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E126" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
+          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant level</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B127" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C127" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Charlotte, NC, US USA</t>
         </is>
       </c>
       <c r="D127" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E127" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B128" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C128" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Central, LA, US USA</t>
         </is>
       </c>
       <c r="D128" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E128" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F128" t="inlineStr">
@@ -4906,32 +4906,32 @@
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="inlineStr">
         <is>
-          <t>Senior Specialist - Architecture</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>LTM Limited</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D129" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Jenkins, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
@@ -4941,32 +4941,32 @@
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4bc906c390155312</t>
+          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B130" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C130" t="inlineStr">
         <is>
-          <t>Rockville, MD, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D130" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E130" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F130" t="inlineStr">
@@ -4976,32 +4976,32 @@
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f57865e75c379265</t>
+          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
         </is>
       </c>
       <c r="B131" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C131" t="inlineStr">
         <is>
-          <t>McLean, VA, US USA</t>
+          <t>Philadelphia, PA, US USA</t>
         </is>
       </c>
       <c r="D131" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E131" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F131" t="inlineStr">
@@ -5011,32 +5011,32 @@
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=55f8300de4fecb0f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f91c24f3a7633e7</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t>Senior Software Engineer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B132" t="inlineStr">
         <is>
-          <t>FINRA</t>
+          <t>Sona</t>
         </is>
       </c>
       <c r="C132" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D132" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E132" t="inlineStr">
         <is>
-          <t>AWS, Lambda, Step Functions, S3, SQS, SNS, ECS, RDS, Scala, NoSQL</t>
+          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F132" t="inlineStr">
@@ -5046,32 +5046,32 @@
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=45adc4c2b25c26f7</t>
+          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>Senior Software Engineer - Analytics Platform</t>
+          <t>Software Engineer – Remote Opportunities</t>
         </is>
       </c>
       <c r="B133" t="inlineStr">
         <is>
-          <t>Bloomberg</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C133" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D133" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E133" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, PostgreSQL, CI/CD, Jenkins, Docker, Kubernetes, Jenkins, SonarQube</t>
+          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
         </is>
       </c>
       <c r="F133" t="inlineStr">
@@ -5081,2072 +5081,42 @@
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=52bd230153d8b27f</t>
+          <t>https://www.indeed.com/viewjob?jk=a59520fbf843f452</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>Senior Software Engineer I-II, Integration Platform Engineering</t>
+          <t>Associate Developer</t>
         </is>
       </c>
       <c r="B134" t="inlineStr">
         <is>
-          <t>Frontline Education</t>
+          <t>Bealls Inc.</t>
         </is>
       </c>
       <c r="C134" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Bradenton, FL, US USA</t>
         </is>
       </c>
       <c r="D134" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E134" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, RDS, Scala, Kafka, Data Modeling</t>
+          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
         </is>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-06-17</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5777ab28ff195025</t>
-        </is>
-      </c>
-    </row>
-    <row r="135">
-      <c r="A135" t="inlineStr">
-        <is>
-          <t>Data Engineer</t>
-        </is>
-      </c>
-      <c r="B135" t="inlineStr">
-        <is>
-          <t>Orion Innovation</t>
-        </is>
-      </c>
-      <c r="C135" t="inlineStr">
-        <is>
-          <t>Montvale, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D135" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E135" t="inlineStr">
-        <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
-        </is>
-      </c>
-      <c r="F135" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G135" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
-        </is>
-      </c>
-    </row>
-    <row r="136">
-      <c r="A136" t="inlineStr">
-        <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>GM Financial</t>
-        </is>
-      </c>
-      <c r="C136" t="inlineStr">
-        <is>
-          <t>Arlington, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D136" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G136" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
-        </is>
-      </c>
-    </row>
-    <row r="137">
-      <c r="A137" t="inlineStr">
-        <is>
-          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
-        </is>
-      </c>
-      <c r="B137" t="inlineStr">
-        <is>
-          <t>Egen Solutions Inc</t>
-        </is>
-      </c>
-      <c r="C137" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D137" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E137" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F137" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G137" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
-        </is>
-      </c>
-    </row>
-    <row r="138">
-      <c r="A138" t="inlineStr">
-        <is>
-          <t>Senior DevOps Engineer</t>
-        </is>
-      </c>
-      <c r="B138" t="inlineStr">
-        <is>
-          <t>accrete</t>
-        </is>
-      </c>
-      <c r="C138" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D138" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E138" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F138" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G138" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
-        </is>
-      </c>
-    </row>
-    <row r="139">
-      <c r="A139" t="inlineStr">
-        <is>
-          <t>Integration Developer</t>
-        </is>
-      </c>
-      <c r="B139" t="inlineStr">
-        <is>
-          <t>Kyocera Document Solutions America, Inc.</t>
-        </is>
-      </c>
-      <c r="C139" t="inlineStr">
-        <is>
-          <t>Fairfield, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D139" t="n">
-        <v>11.1</v>
-      </c>
-      <c r="E139" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
-        </is>
-      </c>
-      <c r="F139" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G139" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
-        </is>
-      </c>
-    </row>
-    <row r="140">
-      <c r="A140" t="inlineStr">
-        <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
-        </is>
-      </c>
-      <c r="B140" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C140" t="inlineStr">
-        <is>
-          <t>Columbus, OH, US USA</t>
-        </is>
-      </c>
-      <c r="D140" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E140" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F140" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G140" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
-        </is>
-      </c>
-    </row>
-    <row r="141">
-      <c r="A141" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B141" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C141" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D141" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E141" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F141" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G141" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
-        </is>
-      </c>
-    </row>
-    <row r="142">
-      <c r="A142" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B142" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C142" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D142" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E142" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F142" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G142" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
-        </is>
-      </c>
-    </row>
-    <row r="143">
-      <c r="A143" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B143" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C143" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D143" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E143" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F143" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G143" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
-        </is>
-      </c>
-    </row>
-    <row r="144">
-      <c r="A144" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B144" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C144" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D144" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E144" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F144" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G144" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
-        </is>
-      </c>
-    </row>
-    <row r="145">
-      <c r="A145" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B145" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C145" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D145" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E145" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F145" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G145" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
-        </is>
-      </c>
-    </row>
-    <row r="146">
-      <c r="A146" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
-        </is>
-      </c>
-      <c r="B146" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C146" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D146" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E146" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F146" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G146" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="147">
-      <c r="A147" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B147" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C147" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D147" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E147" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F147" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G147" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
-        </is>
-      </c>
-    </row>
-    <row r="148">
-      <c r="A148" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B148" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C148" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D148" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E148" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F148" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G148" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
-        </is>
-      </c>
-    </row>
-    <row r="149">
-      <c r="A149" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B149" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C149" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D149" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E149" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F149" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G149" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
-        </is>
-      </c>
-    </row>
-    <row r="150">
-      <c r="A150" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B150" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C150" t="inlineStr">
-        <is>
-          <t>Central, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D150" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E150" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F150" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G150" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="151">
-      <c r="A151" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B151" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C151" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D151" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E151" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F151" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G151" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
-        </is>
-      </c>
-    </row>
-    <row r="152">
-      <c r="A152" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C152" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D152" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="153">
-      <c r="A153" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C153" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D153" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="154">
-      <c r="A154" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B154" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C154" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D154" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E154" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F154" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G154" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
-        </is>
-      </c>
-    </row>
-    <row r="155">
-      <c r="A155" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B155" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C155" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D155" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E155" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F155" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G155" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="156">
-      <c r="A156" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B156" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C156" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D156" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E156" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F156" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G156" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
-        </is>
-      </c>
-    </row>
-    <row r="157">
-      <c r="A157" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B157" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C157" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D157" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E157" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F157" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G157" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="158">
-      <c r="A158" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B158" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C158" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D158" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E158" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F158" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G158" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
-        </is>
-      </c>
-    </row>
-    <row r="159">
-      <c r="A159" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B159" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C159" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D159" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E159" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F159" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G159" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
-        </is>
-      </c>
-    </row>
-    <row r="160">
-      <c r="A160" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B160" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C160" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D160" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E160" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F160" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G160" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="161">
-      <c r="A161" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B161" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C161" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D161" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E161" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F161" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G161" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
-        </is>
-      </c>
-    </row>
-    <row r="162">
-      <c r="A162" t="inlineStr">
-        <is>
-          <t>Sr. Associate Data Engineer</t>
-        </is>
-      </c>
-      <c r="B162" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C162" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D162" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E162" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F162" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G162" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
-        </is>
-      </c>
-    </row>
-    <row r="163">
-      <c r="A163" t="inlineStr">
-        <is>
-          <t>AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>Syracuse University</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>Syracuse, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D163" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="164">
-      <c r="A164" t="inlineStr">
-        <is>
-          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
-        </is>
-      </c>
-      <c r="B164" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C164" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D164" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E164" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F164" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G164" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="165">
-      <c r="A165" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B165" t="inlineStr">
-        <is>
-          <t>INROADS</t>
-        </is>
-      </c>
-      <c r="C165" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D165" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E165" t="inlineStr">
-        <is>
-          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F165" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G165" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="166">
-      <c r="A166" t="inlineStr">
-        <is>
-          <t>Senior Data Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B166" t="inlineStr">
-        <is>
-          <t>Bevi</t>
-        </is>
-      </c>
-      <c r="C166" t="inlineStr">
-        <is>
-          <t>Charlestown, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D166" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E166" t="inlineStr">
-        <is>
-          <t>Kinesis, RDS, Spark, Scala, Kafka, Snowflake, Data Modeling, dbt, CI/CD, AKS</t>
-        </is>
-      </c>
-      <c r="F166" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G166" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=88024c4609faee60</t>
-        </is>
-      </c>
-    </row>
-    <row r="167">
-      <c r="A167" t="inlineStr">
-        <is>
-          <t>Snowflake Architect</t>
-        </is>
-      </c>
-      <c r="B167" t="inlineStr">
-        <is>
-          <t>merican Inc</t>
-        </is>
-      </c>
-      <c r="C167" t="inlineStr">
-        <is>
-          <t>Houston, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D167" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E167" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Scala, Snowflake, Data Modeling, ETL, ELT, dbt, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F167" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G167" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0e555efa8f72b69a</t>
-        </is>
-      </c>
-    </row>
-    <row r="168">
-      <c r="A168" t="inlineStr">
-        <is>
-          <t>IT Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B168" t="inlineStr">
-        <is>
-          <t>Hackensack Meridian Health</t>
-        </is>
-      </c>
-      <c r="C168" t="inlineStr">
-        <is>
-          <t>Iselin, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D168" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E168" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F168" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G168" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="169">
-      <c r="A169" t="inlineStr">
-        <is>
-          <t>Senior Systems &amp; Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B169" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C169" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D169" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E169" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F169" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G169" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="170">
-      <c r="A170" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B170" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C170" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D170" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E170" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F170" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G170" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
-        </is>
-      </c>
-    </row>
-    <row r="171">
-      <c r="A171" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B171" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C171" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D171" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E171" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F171" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G171" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
-        </is>
-      </c>
-    </row>
-    <row r="172">
-      <c r="A172" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B172" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C172" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D172" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E172" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F172" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G172" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
-        </is>
-      </c>
-    </row>
-    <row r="173">
-      <c r="A173" t="inlineStr">
-        <is>
-          <t>Senior AI Driven Test Automation Architect</t>
-        </is>
-      </c>
-      <c r="B173" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
-        </is>
-      </c>
-      <c r="C173" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D173" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E173" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F173" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G173" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
-        </is>
-      </c>
-    </row>
-    <row r="174">
-      <c r="A174" t="inlineStr">
-        <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
-        </is>
-      </c>
-      <c r="B174" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C174" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D174" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E174" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F174" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G174" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="175">
-      <c r="A175" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B175" t="inlineStr">
-        <is>
-          <t>Sona</t>
-        </is>
-      </c>
-      <c r="C175" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D175" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E175" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F175" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G175" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
-        </is>
-      </c>
-    </row>
-    <row r="176">
-      <c r="A176" t="inlineStr">
-        <is>
-          <t>Software Engineer – Remote Opportunities</t>
-        </is>
-      </c>
-      <c r="B176" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C176" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D176" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E176" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F176" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G176" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a59520fbf843f452</t>
-        </is>
-      </c>
-    </row>
-    <row r="177">
-      <c r="A177" t="inlineStr">
-        <is>
-          <t>Java Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B177" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C177" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D177" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E177" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F177" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G177" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5588d97b0802dcb7</t>
-        </is>
-      </c>
-    </row>
-    <row r="178">
-      <c r="A178" t="inlineStr">
-        <is>
-          <t>Senior Java Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B178" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C178" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D178" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E178" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F178" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G178" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2d3dc1e92354e313</t>
-        </is>
-      </c>
-    </row>
-    <row r="179">
-      <c r="A179" t="inlineStr">
-        <is>
-          <t>Senior Java Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B179" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C179" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D179" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E179" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F179" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G179" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=b6bf738c60c62b8d</t>
-        </is>
-      </c>
-    </row>
-    <row r="180">
-      <c r="A180" t="inlineStr">
-        <is>
-          <t>Java Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B180" t="inlineStr">
-        <is>
-          <t>Capgemini</t>
-        </is>
-      </c>
-      <c r="C180" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D180" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E180" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Oracle, Splunk, CI/CD, Jenkins, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F180" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G180" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=76a0805af660a7db</t>
-        </is>
-      </c>
-    </row>
-    <row r="181">
-      <c r="A181" t="inlineStr">
-        <is>
-          <t>Quality Assurance Specialist</t>
-        </is>
-      </c>
-      <c r="B181" t="inlineStr">
-        <is>
-          <t>RELI Group Inc</t>
-        </is>
-      </c>
-      <c r="C181" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D181" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E181" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F181" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G181" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
-        </is>
-      </c>
-    </row>
-    <row r="182">
-      <c r="A182" t="inlineStr">
-        <is>
-          <t>Associate Developer</t>
-        </is>
-      </c>
-      <c r="B182" t="inlineStr">
-        <is>
-          <t>Bealls Inc.</t>
-        </is>
-      </c>
-      <c r="C182" t="inlineStr">
-        <is>
-          <t>Bradenton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D182" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E182" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F182" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G182" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=723d8dc3606ce87f</t>
-        </is>
-      </c>
-    </row>
-    <row r="183">
-      <c r="A183" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B183" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C183" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D183" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E183" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F183" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G183" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
-        </is>
-      </c>
-    </row>
-    <row r="184">
-      <c r="A184" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B184" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C184" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D184" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E184" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F184" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G184" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
-        </is>
-      </c>
-    </row>
-    <row r="185">
-      <c r="A185" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B185" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C185" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D185" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E185" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F185" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G185" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
-        </is>
-      </c>
-    </row>
-    <row r="186">
-      <c r="A186" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B186" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C186" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D186" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E186" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F186" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G186" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
-        </is>
-      </c>
-    </row>
-    <row r="187">
-      <c r="A187" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B187" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C187" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D187" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E187" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F187" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G187" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
-        </is>
-      </c>
-    </row>
-    <row r="188">
-      <c r="A188" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B188" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C188" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D188" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E188" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F188" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G188" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="189">
-      <c r="A189" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B189" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C189" t="inlineStr">
-        <is>
-          <t>Central, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D189" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E189" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F189" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G189" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="190">
-      <c r="A190" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B190" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C190" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D190" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E190" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F190" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G190" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
-        </is>
-      </c>
-    </row>
-    <row r="191">
-      <c r="A191" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B191" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C191" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D191" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E191" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F191" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G191" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
-        </is>
-      </c>
-    </row>
-    <row r="192">
-      <c r="A192" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B192" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C192" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D192" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E192" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F192" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G192" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f91c24f3a7633e7</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-24.xlsx
+++ b/results/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G134"/>
+  <dimension ref="A1:G88"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -923,25 +923,25 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Hadoop Solutions Developer</t>
+          <t>Software Engineer III-Databricks</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Wilmington, DE, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>20.8</v>
+        <v>18.8</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, RDS, Azure, Databricks, BigQuery, Hadoop, HDFS, Hive, Sqoop</t>
+          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
@@ -951,32 +951,32 @@
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5b43cb1da9bd5e66</t>
+          <t>https://www.indeed.com/viewjob?jk=4788de97836b6e30</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Software Engineer III-Databricks</t>
+          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.8</v>
+        <v>18.1</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,24 +986,24 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4788de97836b6e30</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>AWS Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>UCLA Health</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
@@ -1011,77 +1011,77 @@
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6bea0599e34ce74e</t>
+          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>Continuum Media Network Inc</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
+          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
@@ -1091,67 +1091,67 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
+          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AWS Solutions Architect</t>
+          <t>Senior Machine Learning Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Siemens</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>18.1</v>
+        <v>17.4</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Redshift, S3, ECS, IAM, RDS, Scala</t>
+          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, IAM, RDS, Spark, Scala</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-01-21</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ca7ef41ca26d3ec</t>
+          <t>https://www.indeed.com/viewjob?jk=b019316b66042eb5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Continuum Media Network Inc</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
@@ -1161,32 +1161,32 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
+          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Aurora, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,67 +1196,67 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
+          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>17.4</v>
+        <v>16.7</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b019316b66042eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16.7</v>
+        <v>16</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,32 +1266,32 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
+          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior Data Engineer - Ad Serving</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,67 +1301,67 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
+          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>16.7</v>
+        <v>15.3</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
+          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
+          <t>Platform Engineer IV</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>16</v>
+        <v>15.3</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
@@ -1371,24 +1371,24 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Ad Serving</t>
+          <t>Data Quality Analyst</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>BBQ Holdings</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,7 +1396,7 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
+          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Platform Engineer IV</t>
+          <t>Senior Software Developer, Automation</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,67 +1441,67 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
+          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Quality Analyst</t>
+          <t>Data Architect</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>BBQ Holdings</t>
+          <t>Bagel Brands</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Brooklyn Center, MN, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
+          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Software Engineerâ€“ Full Stack</t>
+          <t>Senior Software Engineer, Data Acquisition</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Cisco</t>
+          <t>People Data Labs</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>San Jose, CA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, PostgreSQL, Data Modeling, CI/CD</t>
+          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,94 +1511,94 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=845b1ae798305d08</t>
+          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Software Developer, Automation</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Bagel Brands</t>
+          <t>Citizens</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Brooklyn Center, MN, US USA</t>
+          <t>Johnston, RI, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
+          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Acquisition</t>
+          <t>Senior QA Engineer - Airvoyant</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>People Data Labs</t>
+          <t>TRAX USA Corp.</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Coral Gables, FL, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,32 +1616,32 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
+          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,32 +1651,32 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Cloud Solutions Engineer – Azure</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,67 +1686,67 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f56342ea02089099</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Senior QA Engineer - Airvoyant</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Coral Gables, FL, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,24 +1756,24 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
+          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>AWS/EKS Platform Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
@@ -1781,34 +1781,34 @@
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,112 +1816,112 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer - 3</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS/EKS Platform Engineer</t>
+          <t>AWS Cloud AI Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Boston Medical Center</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
@@ -1931,67 +1931,67 @@
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>OCI Solutions Architect</t>
+          <t>AI/ML Ops and Data Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, GCP, Hive, Oracle, MySQL, CI/CD, Jenkins</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1e360996f49b9bba</t>
+          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Application Developer</t>
+          <t>Machine Learning Ops Data Engineer</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>New York City Department of Citywide Administrative Services</t>
+          <t>Charles Schwab</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Southlake, TX, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Scala, SQL Server, MongoDB, Azure Cosmos DB, NoSQL, ETL, CI/CD</t>
+          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,59 +2001,59 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8959b284cfe01ae8</t>
+          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Sr. Forward Deployed Engineer</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Cohere Health</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
+          <t>https://www.indeed.com/viewjob?jk=e00458dd00ce6b98</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Software Engineer - 3</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Centerprism</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,29 +2061,29 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b3e11011f10bd71</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>AWS Cloud AI Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>AI/ML Ops and Data Engineer</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,7 +2131,7 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,24 +2141,24 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
+          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Machine Learning Ops Data Engineer</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
+          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Enterprise ServiceNow Architect</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,42 +2201,42 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dc18d561962fcd21</t>
+          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Enterprise Data Architect</t>
+          <t>Associate Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, Kinesis, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=20d65d994c35df77</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,67 +2281,67 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00458dd00ce6b98</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE)</t>
+          <t>AI Solutions Architect | US</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,102 +2351,102 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
+          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Cronisys IT LLC</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Optimum Data Modeler - BSS Transformation</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Kafka, Snowflake, Data Modeling</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,54 +2456,54 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5993c3ad81ad4c85</t>
+          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Python Software Architect</t>
+          <t>Software Development Engineer - Workday Everywhere</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Workday</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Boulder, CO, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, Glue, S3, RDS, Scala, Oracle, SQL Server, PostgreSQL, DynamoDB, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d70d40d60ab2d22</t>
+          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>AI Solutions Architect | US</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -2512,46 +2512,46 @@
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,59 +2561,59 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
+          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Cronisys IT LLC</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
@@ -2621,7 +2621,7 @@
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,34 +2656,34 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
+          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Workday Everywhere</t>
+          <t>Clinical Data Engineer (Application Engineer)</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>Oregon Health &amp; Science University</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,24 +2701,24 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
+          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>San Francisco, CA, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,24 +2736,24 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=11faba3dd5ac31a8</t>
+          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Digital Native Business</t>
+          <t>Software Engineer III - PA085</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>ZoomInfo</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Mountain View, CA, US USA</t>
+          <t>Waltham, MA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c66df27b133d802</t>
+          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Senior Pre-Sales Solution Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,34 +2796,34 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=07d9c465438bd1d6</t>
+          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
+          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>SW Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
+          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Clinical Data Engineer (Application Engineer)</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Oregon Health &amp; Science University</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
+          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,34 +2971,34 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer III - PA085</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>Kyocera Document Solutions America, Inc.</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Fairfield, NJ, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,7 +3006,7 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
@@ -3016,67 +3016,67 @@
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Durham, NC, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b234271097cd37b1</t>
+          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Applied Machine Learning Engineer</t>
+          <t>Sr. Associate Data Engineer</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Vulcan Elements</t>
+          <t>McKesson</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Benson, NC, US USA</t>
+          <t>Overland Park, KS, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, SQL Server, PostgreSQL, Data Modeling, ETL, ELT</t>
+          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,19 +3086,19 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=16fc450b1d33691a</t>
+          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Test Automation Engineer</t>
+          <t>Senior Systems &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -3107,11 +3107,11 @@
         </is>
       </c>
       <c r="D77" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Jenkins, Git</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
@@ -3121,67 +3121,67 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f73b61f08926eb79</t>
+          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant level</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>IT Cloud Architect</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C79" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D79" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E79" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F79" t="inlineStr">
@@ -3191,67 +3191,67 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D80" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
+          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C81" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D81" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E81" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F81" t="inlineStr">
@@ -3261,32 +3261,32 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D82" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E82" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F82" t="inlineStr">
@@ -3296,32 +3296,32 @@
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
+          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Senior Application Engineer- Python/JavaScript/Typescript</t>
+          <t>Senior AI Driven Test Automation Architect</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Egen Solutions Inc</t>
+          <t>Hewlett Packard Enterprise | HPE</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Jose, CA, US USA</t>
         </is>
       </c>
       <c r="D83" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E83" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
         </is>
       </c>
       <c r="F83" t="inlineStr">
@@ -3331,67 +3331,67 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b50cf2a5112831c1</t>
+          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>Senior DevOps Engineer</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>accrete</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C84" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D84" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E84" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cf2219ca946f5e65</t>
+          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Software Engineer</t>
         </is>
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>Kyocera Document Solutions America, Inc.</t>
+          <t>Sona</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>Fairfield, NJ, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D85" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E85" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F85" t="inlineStr">
@@ -3401,24 +3401,24 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C86" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D86" t="n">
@@ -3426,7 +3426,7 @@
       </c>
       <c r="E86" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
         </is>
       </c>
       <c r="F86" t="inlineStr">
@@ -3436,24 +3436,24 @@
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
+          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Quality Assurance Specialist</t>
         </is>
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D87" t="n">
@@ -3461,7 +3461,7 @@
       </c>
       <c r="E87" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F87" t="inlineStr">
@@ -3471,14 +3471,14 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9aaae90b6827622e</t>
+          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B88" t="inlineStr">
@@ -3488,7 +3488,7 @@
       </c>
       <c r="C88" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D88" t="n">
@@ -3506,1617 +3506,7 @@
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebcd57b3de525cca</t>
-        </is>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C89" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D89" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E89" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F89" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G89" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2695d1c25372f189</t>
-        </is>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C90" t="inlineStr">
-        <is>
-          <t>CA, US USA</t>
-        </is>
-      </c>
-      <c r="D90" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E90" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F90" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a70f58838e2cd34a</t>
-        </is>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E91" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F91" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G91" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c76908ce37a5afa9</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Manufacturing</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C92" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D92" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E92" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F92" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G92" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=711e6d671e6ce6cc</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C93" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D93" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E93" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F93" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G93" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=f8ecd830bc50ddf8</t>
-        </is>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C94" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D94" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E94" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F94" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G94" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c89d85a8acffb186</t>
-        </is>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C95" t="inlineStr">
-        <is>
-          <t>Denver, CO, US USA</t>
-        </is>
-      </c>
-      <c r="D95" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E95" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F95" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G95" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=62aa67ffee10afa8</t>
-        </is>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>Central, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E96" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F96" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G96" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=51ee72135fd523f3</t>
-        </is>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E97" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F97" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G97" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=65c6771565c401be</t>
-        </is>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C98" t="inlineStr">
-        <is>
-          <t>Raleigh, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D98" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E98" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F98" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G98" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e3a205268ca815d6</t>
-        </is>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C99" t="inlineStr">
-        <is>
-          <t>Los Angeles, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D99" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E99" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F99" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G99" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e4df7b403eedd3f2</t>
-        </is>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C100" t="inlineStr">
-        <is>
-          <t>Austin, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D100" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E100" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F100" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G100" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e1d5ec05338e5307</t>
-        </is>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C101" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D101" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E101" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F101" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G101" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=1a27f3fed1cb92a2</t>
-        </is>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C102" t="inlineStr">
-        <is>
-          <t>Mountain View, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D102" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E102" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F102" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G102" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c8697154f8ab7b59</t>
-        </is>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C103" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D103" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E103" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=2febc928d422bbaf</t>
-        </is>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C104" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D104" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E104" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c0a886cb5fb87382</t>
-        </is>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Communications, Media, Entertainment &amp; Games</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C105" t="inlineStr">
-        <is>
-          <t>San Francisco, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D105" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E105" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=577681ccb90f5217</t>
-        </is>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C106" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D106" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E106" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=9cd6a537b32a4a4c</t>
-        </is>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Retail</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C107" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D107" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E107" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e122255a8b305e22</t>
-        </is>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Container Platform Engineer</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C108" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D108" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E108" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, Terraform, Kubernetes, Jenkins</t>
-        </is>
-      </c>
-      <c r="F108" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G108" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=5b12ac3bb4713b71</t>
-        </is>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Sr. Associate Data Engineer</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>McKesson</t>
-        </is>
-      </c>
-      <c r="C109" t="inlineStr">
-        <is>
-          <t>Overland Park, KS, US USA</t>
-        </is>
-      </c>
-      <c r="D109" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E109" t="inlineStr">
-        <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F109" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G109" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
-        </is>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>AI Data Engineer</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Syracuse University</t>
-        </is>
-      </c>
-      <c r="C110" t="inlineStr">
-        <is>
-          <t>Syracuse, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D110" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E110" t="inlineStr">
-        <is>
-          <t>AWS, Azure, Data Factory, GCP, Scala, Data Modeling, Power BI, Docker, Kubernetes, Python</t>
-        </is>
-      </c>
-      <c r="F110" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G110" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0dfd015014ed5a6b</t>
-        </is>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Senior AI ML Software Engineer - Data Platforms - Remote Nationwide or Hybrid in MN or DC</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Optum</t>
-        </is>
-      </c>
-      <c r="C111" t="inlineStr">
-        <is>
-          <t>Eden Prairie, MN, US USA</t>
-        </is>
-      </c>
-      <c r="D111" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E111" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Scala, Snowflake, Power BI, CI/CD, Git</t>
-        </is>
-      </c>
-      <c r="F111" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G111" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=afcebdc1e96b80ec</t>
-        </is>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Data Engineer I</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>INROADS</t>
-        </is>
-      </c>
-      <c r="C112" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D112" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E112" t="inlineStr">
-        <is>
-          <t>RDS, Snowflake, Dimensional Modeling, Kimball, Snowflake Schema, ETL, ELT, dbt, CI/CD, GitHub Actions</t>
-        </is>
-      </c>
-      <c r="F112" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G112" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=293dbef0165a4bbf</t>
-        </is>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Senior Systems &amp; Backend Engineer</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C113" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D113" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E113" t="inlineStr">
-        <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F113" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G113" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
-        </is>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>IT Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Hackensack Meridian Health</t>
-        </is>
-      </c>
-      <c r="C114" t="inlineStr">
-        <is>
-          <t>Iselin, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D114" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Java Application Architect</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>BV Teck</t>
-        </is>
-      </c>
-      <c r="C115" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D115" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C116" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D116" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C117" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D117" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E117" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F117" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G117" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
-        </is>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C118" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D118" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E118" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F118" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G118" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
-        </is>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Senior AI Driven Test Automation Architect</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
-        </is>
-      </c>
-      <c r="C119" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D119" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E119" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F119" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G119" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
-        </is>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C120" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D120" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E120" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F120" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G120" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="121">
-      <c r="A121" t="inlineStr">
-        <is>
-          <t>Quality Assurance Specialist</t>
-        </is>
-      </c>
-      <c r="B121" t="inlineStr">
-        <is>
-          <t>RELI Group Inc</t>
-        </is>
-      </c>
-      <c r="C121" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D121" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E121" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F121" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G121" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
-        </is>
-      </c>
-    </row>
-    <row r="122">
-      <c r="A122" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B122" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C122" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D122" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E122" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F122" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G122" t="inlineStr">
-        <is>
           <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
-        </is>
-      </c>
-    </row>
-    <row r="123">
-      <c r="A123" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B123" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C123" t="inlineStr">
-        <is>
-          <t>Dallas, TX, US USA</t>
-        </is>
-      </c>
-      <c r="D123" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E123" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F123" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G123" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=19f65e5ec0ffd488</t>
-        </is>
-      </c>
-    </row>
-    <row r="124">
-      <c r="A124" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B124" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C124" t="inlineStr">
-        <is>
-          <t>Boston, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D124" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E124" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F124" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G124" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=431da68150f3291d</t>
-        </is>
-      </c>
-    </row>
-    <row r="125">
-      <c r="A125" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B125" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C125" t="inlineStr">
-        <is>
-          <t>Atlanta, GA, US USA</t>
-        </is>
-      </c>
-      <c r="D125" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E125" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F125" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G125" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3272846d5260e885</t>
-        </is>
-      </c>
-    </row>
-    <row r="126">
-      <c r="A126" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B126" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C126" t="inlineStr">
-        <is>
-          <t>Washington, DC, US USA</t>
-        </is>
-      </c>
-      <c r="D126" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E126" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G126" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=44a83bfac7754702</t>
-        </is>
-      </c>
-    </row>
-    <row r="127">
-      <c r="A127" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B127" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C127" t="inlineStr">
-        <is>
-          <t>Charlotte, NC, US USA</t>
-        </is>
-      </c>
-      <c r="D127" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E127" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F127" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G127" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=d6c5660e8705aa9c</t>
-        </is>
-      </c>
-    </row>
-    <row r="128">
-      <c r="A128" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B128" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C128" t="inlineStr">
-        <is>
-          <t>Central, LA, US USA</t>
-        </is>
-      </c>
-      <c r="D128" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E128" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F128" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G128" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cc9a7a66d97e77e2</t>
-        </is>
-      </c>
-    </row>
-    <row r="129">
-      <c r="A129" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B129" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C129" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D129" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E129" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F129" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G129" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=57a2a930cddd393d</t>
-        </is>
-      </c>
-    </row>
-    <row r="130">
-      <c r="A130" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B130" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C130" t="inlineStr">
-        <is>
-          <t>Chicago, IL, US USA</t>
-        </is>
-      </c>
-      <c r="D130" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E130" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F130" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G130" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=bcc8dd4d32558374</t>
-        </is>
-      </c>
-    </row>
-    <row r="131">
-      <c r="A131" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Financial Services</t>
-        </is>
-      </c>
-      <c r="B131" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C131" t="inlineStr">
-        <is>
-          <t>Philadelphia, PA, US USA</t>
-        </is>
-      </c>
-      <c r="D131" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E131" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F131" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G131" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6f91c24f3a7633e7</t>
-        </is>
-      </c>
-    </row>
-    <row r="132">
-      <c r="A132" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B132" t="inlineStr">
-        <is>
-          <t>Sona</t>
-        </is>
-      </c>
-      <c r="C132" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D132" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E132" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F132" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G132" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
-        </is>
-      </c>
-    </row>
-    <row r="133">
-      <c r="A133" t="inlineStr">
-        <is>
-          <t>Software Engineer – Remote Opportunities</t>
-        </is>
-      </c>
-      <c r="B133" t="inlineStr">
-        <is>
-          <t>nan</t>
-        </is>
-      </c>
-      <c r="C133" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D133" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E133" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Oracle, SQL Server, MySQL, MongoDB, CI/CD, Jenkins, Azure DevOps, Jenkins</t>
-        </is>
-      </c>
-      <c r="F133" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G133" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=a59520fbf843f452</t>
-        </is>
-      </c>
-    </row>
-    <row r="134">
-      <c r="A134" t="inlineStr">
-        <is>
-          <t>Associate Developer</t>
-        </is>
-      </c>
-      <c r="B134" t="inlineStr">
-        <is>
-          <t>Bealls Inc.</t>
-        </is>
-      </c>
-      <c r="C134" t="inlineStr">
-        <is>
-          <t>Bradenton, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D134" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E134" t="inlineStr">
-        <is>
-          <t>RDS, Azure, Scala, Data Modeling, ETL, ELT, Power BI, Tableau, Azure DevOps, Git</t>
-        </is>
-      </c>
-      <c r="F134" t="inlineStr">
-        <is>
-          <t>2026-06-17</t>
-        </is>
-      </c>
-      <c r="G134" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=723d8dc3606ce87f</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-24.xlsx
+++ b/results/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G88"/>
+  <dimension ref="A1:G78"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -468,95 +468,95 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Architect</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>Alpharetta, GA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>21.5</v>
+        <v>19.4</v>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Blob Storage, Event Hubs</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=12a7366a5fe55ec4</t>
+          <t>https://www.indeed.com/viewjob?jk=6e5bb3180486d837</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>CVS Health</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Boston, MA, US USA</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>21.5</v>
+        <v>18.1</v>
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5543ba0ab775d610</t>
+          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Continuum Media Network Inc</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>Downers Grove, IL, US USA</t>
+          <t>Denver, CO, US USA</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>21.5</v>
+        <v>17.4</v>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -566,32 +566,32 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a077af88e8069ec7</t>
+          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>University of Colorado</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>Jacksonville, FL, US USA</t>
+          <t>Aurora, CO, US USA</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>21.5</v>
+        <v>17.4</v>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
@@ -601,32 +601,32 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76143d39ee35b355</t>
+          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer, Senior</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Booz Allen Hamilton</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Annapolis, MD, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>21.5</v>
+        <v>16.7</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
@@ -636,67 +636,67 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=f4ed12d88cc2e877</t>
+          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>AWS Cloud Architect</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Cloud and Things</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Providence, RI, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>21.5</v>
+        <v>16.7</v>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, IAM, RDS, Azure, Google Cloud Platform, GCP, Scala, Oracle, Splunk, CI/CD</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=eee1d8b4f35568a7</t>
+          <t>https://www.indeed.com/viewjob?jk=e3a616293a442292</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Richmond, VA, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>21.5</v>
+        <v>16.7</v>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=be6ca4cb28d4f2ab</t>
+          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>21.5</v>
+        <v>16</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820aad6a65dfbe24</t>
+          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Data Engineer - Ad Serving</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Best Buy</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Birmingham, AL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>21.5</v>
+        <v>15.3</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,54 +776,54 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bc1bab104e859e83</t>
+          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer VI - Data Services</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Hartford, CT, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>21.5</v>
+        <v>15.3</v>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=bdd44ba9ec2abfb8</t>
+          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Platform Engineer IV</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Capgemini</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -832,11 +832,11 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>21.5</v>
+        <v>15.3</v>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
@@ -846,32 +846,32 @@
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e5737811adca0295</t>
+          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Quality Analyst</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>BBQ Holdings</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Harrisburg, PA, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>21.5</v>
+        <v>15.3</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
@@ -881,102 +881,102 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5dee030b01228d0d</t>
+          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Kemper</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>21.5</v>
+        <v>14.6</v>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>AWS, Glue, Kinesis, RDS, Azure, Spark, Scala, Kafka, Snowflake, Dimensional Modeling</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=02eb3eef526fbc7e</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Software Engineer III-Databricks</t>
+          <t>Senior Software Developer, Automation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Wilmington, DE, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>18.8</v>
+        <v>14.6</v>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, ECS, RDS, Databricks, Unity Catalog, Spark, PySpark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4788de97836b6e30</t>
+          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior GCP Data Engineer for Patient Safety Measure Engine</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CVS Health</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>18.1</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Vertex AI, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
@@ -986,7 +986,7 @@
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d3f3d22744f5363</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
         </is>
       </c>
     </row>
@@ -998,300 +998,300 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>UCLA Health</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>18.1</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, GCP, Spark, Scala, Snowflake, Oracle</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d071a80499173a38</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Continuum Media Network Inc</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Denver, CO, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>AWS, Redshift, Athena, ECS, RDS, Azure, GCP, Scala, SQL Server, MySQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d00a5640ed9db41</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>University of Colorado</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Aurora, CO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, RDS, Azure, Data Factory, Databricks, Scala, Snowflake, SQL Server</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b0851f406bcf6538</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Senior Machine Learning Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Siemens</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>17.4</v>
+        <v>13.2</v>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>AWS, EMR, Lambda, Step Functions, S3, ECS, IAM, RDS, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-01-21</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b019316b66042eb5</t>
+          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>16.7</v>
+        <v>13.2</v>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
+          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>16.7</v>
+        <v>13.2</v>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4043ee460a725672</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>16.7</v>
+        <v>13.2</v>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>16</v>
+        <v>13.2</v>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Ad Serving</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
@@ -1301,102 +1301,102 @@
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
+          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Platform Engineer VI - Data Services</t>
+          <t>AWS/EKS Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=530025f520e267c1</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Platform Engineer IV</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Capgemini</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Glue, EMR, Athena, S3, IAM, RDS, Spark, Scala, Kafka</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3a6f5499c457885c</t>
+          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Data Quality Analyst</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>BBQ Holdings</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>15.3</v>
+        <v>13.2</v>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
@@ -1406,32 +1406,32 @@
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
+          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Senior Software Developer, Automation</t>
+          <t>Software Engineer - 3</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,84 +1441,84 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
+          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Data Architect</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Bagel Brands</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Brooklyn Center, MN, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>14.6</v>
+        <v>12.5</v>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Spark, Scala, Snowflake, Data Modeling, Dimensional Modeling</t>
+          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4192bfe41a15fbd0</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Software Engineer, Data Acquisition</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>People Data Labs</t>
+          <t>Centerprism</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, Redshift, SQS, RDS, Azure, Databricks, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=5ce03f58dc0c9d18</t>
+          <t>https://www.indeed.com/viewjob?jk=7b3e11011f10bd71</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
@@ -1532,11 +1532,11 @@
         </is>
       </c>
       <c r="D32" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,32 +1546,32 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Technology Risk Senior Analyst- Data, AI and Emerging Technology</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Citizens</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Johnston, RI, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, IAM, RDS, Azure, Scala, Oracle, ETL, ELT, Talend, Tableau</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,32 +1581,32 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e522509d51c4142a</t>
+          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Senior QA Engineer - Airvoyant</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>TRAX USA Corp.</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Coral Gables, FL, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>13.9</v>
+        <v>12.5</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SQS, SNS, API Gateway, IAM, RDS, Scala, SQL Server</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,67 +1616,67 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=38ee81c497706d67</t>
+          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Scientist</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>ecoATM LLC</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>San Diego, CA, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
+          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Associate Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>AWS, Kinesis, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,32 +1686,32 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
@@ -1721,32 +1721,32 @@
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
@@ -1756,32 +1756,32 @@
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AWS/EKS Platform Engineer</t>
+          <t>AI Solutions Architect | US</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>13.2</v>
+        <v>11.8</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
@@ -1791,242 +1791,242 @@
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>13.2</v>
+        <v>11.1</v>
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Software Engineer - 3</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Cronisys IT LLC</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>AWS Cloud AI Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Boston Medical Center</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, SNS, RDS, Scala, CI/CD, GitHub Actions, AWS CodePipeline, Terraform</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c7b96f6d08eb2e5b</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>AI/ML Ops and Data Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cdb594873fc1ad66</t>
+          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Machine Learning Ops Data Engineer</t>
+          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Charles Schwab</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Southlake, TX, US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>IAM, RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Vertex AI, Scala, Data Modeling, MLOps</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=33e84a2e009cf57d</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Cohere Health</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>Boston, MA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, IAM, RDS, PostgreSQL, MongoDB, DynamoDB</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
@@ -2036,32 +2036,32 @@
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e00458dd00ce6b98</t>
+          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Centerprism</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
@@ -2071,19 +2071,19 @@
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b3e11011f10bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Clinical Data Engineer (Application Engineer)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Oregon Health &amp; Science University</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -2092,46 +2092,46 @@
         </is>
       </c>
       <c r="D48" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE)</t>
+          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
@@ -2141,102 +2141,102 @@
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
+          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
+          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
-        <v>12.5</v>
+        <v>11.1</v>
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
+          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Associate Cloud &amp; DevOps Engineer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,32 +2246,32 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Senior Pre-Sales Solution Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,94 +2281,94 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
+          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
+          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>AI Solutions Architect | US</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,7 +2376,7 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
@@ -2386,24 +2386,24 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>SW Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Cronisys IT LLC</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer - Workday Everywhere</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Workday</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Boulder, CO, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=609d27118699b077</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,34 +2516,34 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
+          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,7 +2551,7 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
@@ -2561,24 +2561,24 @@
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>Kyocera Document Solutions America, Inc.</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Fairfield, NJ, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
@@ -2586,42 +2586,42 @@
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,19 +2631,19 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -2652,11 +2652,11 @@
         </is>
       </c>
       <c r="D64" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,19 +2666,19 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Clinical Data Engineer (Application Engineer)</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Oregon Health &amp; Science University</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -2687,116 +2687,116 @@
         </is>
       </c>
       <c r="D65" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Software Engineer III - PA085</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>ZoomInfo</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Waltham, MA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>GCP, BigQuery, Dataflow, Spark, Kafka, Snowflake, Data Modeling, ETL, ELT, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4c411d19dcc80f29</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Pre-Sales Solution Architect</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,102 +2806,102 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Senior Systems &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant level</t>
+          <t>IT Cloud Architect</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
@@ -2911,32 +2911,32 @@
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Solutions Architect (Remote)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>LangChain</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,14 +2946,14 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
+          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
@@ -2963,15 +2963,15 @@
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,59 +2981,59 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
+          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Kyocera Document Solutions America, Inc.</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Fairfield, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Software Engineer II (Python/Java/AWS/Pyspark)</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D75" t="n">
@@ -3041,7 +3041,7 @@
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, PySpark, Scala, Star Schema, CI/CD, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
@@ -3051,24 +3051,24 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=175150f6472dcabf</t>
+          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Sr. Associate Data Engineer</t>
+          <t>Quality Assurance Specialist</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>McKesson</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Overland Park, KS, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Databricks, Scala, Dimensional Modeling, ETL, Talend, Git, CloudWatch</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=037b9d029a6c32da</t>
+          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Backend Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,34 +3111,34 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D78" t="n">
@@ -3146,7 +3146,7 @@
       </c>
       <c r="E78" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F78" t="inlineStr">
@@ -3156,357 +3156,7 @@
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" t="inlineStr">
-        <is>
-          <t>IT Cloud Architect</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>Hackensack Meridian Health</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>Iselin, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E79" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
-        </is>
-      </c>
-      <c r="F79" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G79" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B80" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C80" t="inlineStr">
-        <is>
-          <t>Seattle, WA, US USA</t>
-        </is>
-      </c>
-      <c r="D80" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E80" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F80" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G80" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B81" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C81" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D81" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E81" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F81" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G81" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>Solutions Architect (Remote)</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>LangChain</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>US USA</t>
-        </is>
-      </c>
-      <c r="D82" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E82" t="inlineStr">
-        <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
-        </is>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G82" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=cb19fdabfeceb391</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>Senior AI Driven Test Automation Architect</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Hewlett Packard Enterprise | HPE</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>San Jose, CA, US USA</t>
-        </is>
-      </c>
-      <c r="D83" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E83" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, GCP, Scala, CI/CD, Jenkins, GitHub Actions, Azure DevOps, Docker</t>
-        </is>
-      </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G83" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=4dccf85cb629f63b</t>
-        </is>
-      </c>
-    </row>
-    <row r="84">
-      <c r="A84" t="inlineStr">
-        <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>JPMorganChase</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>Jersey City, NJ, US USA</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E84" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
-        </is>
-      </c>
-      <c r="F84" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G84" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
-        </is>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Software Engineer</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Sona</t>
-        </is>
-      </c>
-      <c r="C85" t="inlineStr">
-        <is>
-          <t>Miami, FL, US USA</t>
-        </is>
-      </c>
-      <c r="D85" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E85" t="inlineStr">
-        <is>
-          <t>AWS, IAM, Azure, Scala, PostgreSQL, MySQL, CI/CD, Docker, Kubernetes, Git</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=0f41a26b73335bac</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Great Gray Trust Company</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D86" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E86" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
-        </is>
-      </c>
-      <c r="F86" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G86" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
-        </is>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Quality Assurance Specialist</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>RELI Group Inc</t>
-        </is>
-      </c>
-      <c r="C87" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D87" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E87" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F87" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G87" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
-        </is>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C88" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D88" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E88" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F88" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G88" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
+          <t>https://www.indeed.com/viewjob?jk=6a9fb68922a90c5c</t>
         </is>
       </c>
     </row>

--- a/results/job_matches_2026-07-24.xlsx
+++ b/results/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G78"/>
+  <dimension ref="A1:G77"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -608,35 +608,35 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Data Engineer, Senior</t>
+          <t>DevOps Engineer Live Streaming- Wixom, MI</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Booz Allen Hamilton</t>
+          <t>J&amp;B Medical</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Wixom, MI, US USA</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>16.7</v>
+        <v>17.4</v>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>AWS, EMR, Redshift, RDS, Azure, Databricks, Hadoop, Hive, Spark, Scala</t>
+          <t>AWS, Lambda, Redshift, Athena, Step Functions, S3, RDS, Azure, GCP, Scala</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c25594297d7dcd08</t>
+          <t>https://www.indeed.com/viewjob?jk=41ea01c619cf5f4e</t>
         </is>
       </c>
     </row>
@@ -888,17 +888,17 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Data engineer (Power BI)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Senior Software Developer, Automation</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,77 +941,77 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Software Developer, Automation</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>13.9</v>
+        <v>14.6</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
+          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.2</v>
+        <v>13.9</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
+          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
+          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>AWS/EKS Platform Engineer</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>AWS/EKS Platform Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,42 +1396,42 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
+          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Software Engineer - 3</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>12.5</v>
+        <v>13.2</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
@@ -1441,24 +1441,24 @@
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
+          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Software Engineer - 3</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>eBay</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Centerprism</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b3e11011f10bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Centerprism</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,7 +1536,7 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
@@ -1546,24 +1546,24 @@
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=7b3e11011f10bd71</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE)</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
@@ -1571,34 +1571,34 @@
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
+          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
@@ -1606,7 +1606,7 @@
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
@@ -1616,24 +1616,24 @@
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
+          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Senior Data Scientist</t>
+          <t>Software Development Engineer II</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>ecoATM LLC</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>San Diego, CA, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
@@ -1641,7 +1641,7 @@
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Redshift, RDS, Databricks, BigQuery, Spark, Snowflake, Data Modeling, ETL, ELT, dbt</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,7 +1651,7 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=462774f83d88a209</t>
+          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
         </is>
       </c>
     </row>
@@ -2148,17 +2148,17 @@
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Artificial Intelligence Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>M2S Group</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Highland Park, IL, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,24 +2176,24 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
+          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2201,7 +2201,7 @@
       </c>
       <c r="E51" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F51" t="inlineStr">
@@ -2211,24 +2211,24 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>PURE Insurance</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2236,7 +2236,7 @@
       </c>
       <c r="E52" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F52" t="inlineStr">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Senior Pre-Sales Solution Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior Pre-Sales Solution Architect</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
+          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>SW Engineer - Sr. Consultant level</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>Visa</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-22</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
+          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant level</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,34 +2446,34 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>Senior Architect</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>United Concordia Dental</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>PA, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,24 +2491,24 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
+          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
@@ -2526,24 +2526,24 @@
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
+          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>GM Financial</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Arlington, TX, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
@@ -2551,17 +2551,17 @@
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
+          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
         </is>
       </c>
     </row>
@@ -2603,25 +2603,25 @@
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>10.4</v>
+        <v>11.1</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,7 +2691,7 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
@@ -2701,7 +2701,7 @@
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
@@ -2743,17 +2743,17 @@
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>DERMS Data Architect &amp; Integration</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D67" t="n">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,19 +2771,19 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
+          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Senior Systems &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
+          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Backend Engineer</t>
+          <t>IT Cloud Architect</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,34 +2831,34 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>IT Cloud Architect</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,34 +2866,34 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=23122d038602c127</t>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Solutions Architect (Remote)</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>LangChain</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,34 +2936,34 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Scala, CI/CD, Terraform, Kubernetes, AKS, Git, Datadog</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ed4c550bf8810c96</t>
+          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2981,24 +2981,24 @@
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Quality Assurance Specialist</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D74" t="n">
@@ -3006,17 +3006,17 @@
       </c>
       <c r="E74" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
+          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
         </is>
       </c>
     </row>
@@ -3058,17 +3058,17 @@
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Quality Assurance Specialist</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>RELI Group Inc</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
         <is>
-          <t>Baltimore, MD, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D76" t="n">
@@ -3076,7 +3076,7 @@
       </c>
       <c r="E76" t="inlineStr">
         <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F76" t="inlineStr">
@@ -3086,24 +3086,24 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
+          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Databricks</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D77" t="n">
@@ -3111,50 +3111,15 @@
       </c>
       <c r="E77" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B78" t="inlineStr">
-        <is>
-          <t>LEADER BANK</t>
-        </is>
-      </c>
-      <c r="C78" t="inlineStr">
-        <is>
-          <t>Arlington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D78" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E78" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, CI/CD, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F78" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G78" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6a9fb68922a90c5c</t>
         </is>

--- a/results/job_matches_2026-07-24.xlsx
+++ b/results/job_matches_2026-07-24.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G77"/>
+  <dimension ref="A1:G73"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -678,17 +678,17 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
+          <t>Business Analyst Specialist</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>NTT DATA</t>
+          <t>Macy's</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Johns Creek, GA, US USA</t>
         </is>
       </c>
       <c r="D8" t="n">
@@ -696,7 +696,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
+          <t>AWS, Glue, Redshift, S3, RDS, Azure, Synapse Analytics, BigQuery, Hadoop, Scala</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -706,32 +706,32 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
+          <t>https://www.indeed.com/viewjob?jk=fa6a87768d5aab6f</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
+          <t>Senior AI DevOps Engineer (AI Ops / Platform Engineering) (Hybrid)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>TELEWORLD SOLUTIONS INC</t>
+          <t>NTT DATA</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>16</v>
+        <v>16.7</v>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
+          <t>AWS, RDS, Azure, Vertex AI, Scala, Splunk, MLOps, MLflow, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
@@ -741,32 +741,32 @@
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
+          <t>https://www.indeed.com/viewjob?jk=179f845817d9c394</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Senior Data Engineer - Ad Serving</t>
+          <t>Data Analyst IV/ Data Scientist AI/ML Specialist</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Best Buy</t>
+          <t>TELEWORLD SOLUTIONS INC</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>15.3</v>
+        <v>16</v>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>AWS, Glue, Lambda, Kinesis, Athena, Step Functions, RDS, GCP, Dataflow, Spark</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Hive, Spark, Snowflake, MongoDB, MLOps</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
@@ -776,7 +776,7 @@
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3751536eef408193</t>
+          <t>https://www.indeed.com/viewjob?jk=968b86a37881afb4</t>
         </is>
       </c>
     </row>
@@ -853,52 +853,52 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Data Quality Analyst</t>
+          <t>Data engineer (Power BI)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>BBQ Holdings</t>
+          <t>Intellibee Inc</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>15.3</v>
+        <v>14.6</v>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Databricks, Unity Catalog, Delta Live Tables, GCP, Spark, PySpark</t>
+          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=43dc646411602558</t>
+          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Data engineer (Power BI)</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Intellibee Inc</t>
+          <t>Pyx Health</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D14" t="n">
@@ -906,7 +906,7 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Synapse Analytics, Databricks, Data Lake Storage, Dataflow, Scala, Snowflake, Oracle</t>
+          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
@@ -916,24 +916,24 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b1c4bb478a10661f</t>
+          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Senior Software Developer, Automation</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Pyx Health</t>
+          <t>FFF Enterprises</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Temecula, CA, US USA</t>
         </is>
       </c>
       <c r="D15" t="n">
@@ -941,77 +941,77 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Unity Catalog, Spark, PySpark, Scala, SQL Server, Data Modeling</t>
+          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8ea50071b5800db9</t>
+          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Senior Software Developer, Automation</t>
+          <t>Azure Cloud Engineer</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>FFF Enterprises</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Temecula, CA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>14.6</v>
+        <v>13.9</v>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Scala, Kafka, SQL Server, PostgreSQL, MySQL, CI/CD</t>
+          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=36278831392884e9</t>
+          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
         </is>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Azure Cloud Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>West Monroe</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>13.9</v>
+        <v>13.2</v>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Data Factory, Synapse Analytics, Event Hubs, Scala, CI/CD, GitHub Actions, Azure DevOps</t>
+          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
@@ -1021,7 +1021,7 @@
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6d24836d15aa901f</t>
+          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
         </is>
       </c>
     </row>
@@ -1038,7 +1038,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>Washington, DC, US USA</t>
         </is>
       </c>
       <c r="D18" t="n">
@@ -1056,7 +1056,7 @@
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=9d7a92b5805d6137</t>
+          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
         </is>
       </c>
     </row>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Washington, DC, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D19" t="n">
@@ -1091,7 +1091,7 @@
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fd3e9bf3427fd2d6</t>
+          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
         </is>
       </c>
     </row>
@@ -1108,7 +1108,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Seattle, WA, US USA</t>
         </is>
       </c>
       <c r="D20" t="n">
@@ -1126,7 +1126,7 @@
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3ec6e06ec6b6e3fa</t>
+          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
         </is>
       </c>
     </row>
@@ -1143,7 +1143,7 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>Seattle, WA, US USA</t>
+          <t>Los Angeles, CA, US USA</t>
         </is>
       </c>
       <c r="D21" t="n">
@@ -1161,24 +1161,24 @@
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=14216a18b53ccbd9</t>
+          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Senior Cloud Data Engineer</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>West Monroe</t>
+          <t>Surescripts</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Los Angeles, CA, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D22" t="n">
@@ -1186,7 +1186,7 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Google Cloud Platform, GCP, Spark, Scala, Snowflake, Data Modeling</t>
+          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
@@ -1196,24 +1196,24 @@
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c4bf15647e9f22c6</t>
+          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Senior Cloud Data Engineer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Surescripts</t>
+          <t>Domino's</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Ann Arbor, MI, US USA</t>
         </is>
       </c>
       <c r="D23" t="n">
@@ -1221,7 +1221,7 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>RDS, Google Cloud Platform, GCP, BigQuery, Dataflow, Cloud Storage, Scala, Data Modeling, Power BI, Tableau</t>
+          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
@@ -1231,24 +1231,24 @@
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d4bcd6e2a9d67464</t>
+          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
         </is>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Data Engineer III</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Domino's</t>
+          <t>Love’s Travel Stops</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>Ann Arbor, MI, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D24" t="n">
@@ -1256,7 +1256,7 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>RDS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, Data Modeling, ETL, ELT</t>
+          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
@@ -1266,24 +1266,24 @@
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8d0c84a27d084fd0</t>
+          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
         </is>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Data Engineer III</t>
+          <t>Data Engineer II</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Love’s Travel Stops</t>
+          <t>First Citizens Bank</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Raleigh, NC, US USA</t>
         </is>
       </c>
       <c r="D25" t="n">
@@ -1291,34 +1291,34 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>RDS, Azure, Scala, Kafka, Snowflake, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcbdf62f4fcd37bb</t>
+          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
         </is>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Data Engineer II</t>
+          <t>AWS/EKS Platform Engineer</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>First Citizens Bank</t>
+          <t>Glint Tech Solutions</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Raleigh, NC, US USA</t>
+          <t>Reston, VA, US USA</t>
         </is>
       </c>
       <c r="D26" t="n">
@@ -1326,7 +1326,7 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>AWS, RDS, Spark, Scala, Snowflake, ETL, ELT, dbt, Power BI, Tableau</t>
+          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
@@ -1336,24 +1336,24 @@
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=34ac40ad9509eb3e</t>
+          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>AWS/EKS Platform Engineer</t>
+          <t>Senior Full Stack Software Engineer</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Glint Tech Solutions</t>
+          <t>Grainger</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Reston, VA, US USA</t>
+          <t>Chicago, IL, US USA</t>
         </is>
       </c>
       <c r="D27" t="n">
@@ -1361,34 +1361,34 @@
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, IAM, Azure, Scala, CI/CD, Jenkins, Terraform, AWS CloudFormation</t>
+          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1db2cf8626316dc6</t>
+          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
         </is>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Senior Full Stack Software Engineer</t>
+          <t>Database Administrator</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Grainger</t>
+          <t>Chipotle Mexican Grill</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Chicago, IL, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D28" t="n">
@@ -1396,69 +1396,69 @@
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>AWS, RDS, GCP, Scala, Kafka, Snowflake, PostgreSQL, ETL, CI/CD, GitHub Actions</t>
+          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3949515f70fcddc9</t>
+          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
         </is>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Database Administrator</t>
+          <t>Senior Systems Engineer - Delivery DevOps</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Chipotle Mexican Grill</t>
+          <t>Intuit</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Atlanta, GA, US USA</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>13.2</v>
+        <v>12.5</v>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Snowflake, Oracle, SQL Server, Data Modeling, ETL, ELT, dbt</t>
+          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1c47582fc7c2ae03</t>
+          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
         </is>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Software Engineer - 3</t>
+          <t>Senior Developer</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>eBay</t>
+          <t>Centerprism</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>St. Louis, MO, US USA</t>
         </is>
       </c>
       <c r="D30" t="n">
@@ -1466,34 +1466,34 @@
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>RDS, Hadoop, Hive, Spark, Scala, Kafka, Oracle, ETL, Docker, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=57e3d41ef9d854b4</t>
+          <t>https://www.indeed.com/viewjob?jk=7b3e11011f10bd71</t>
         </is>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Senior Systems Engineer - Delivery DevOps</t>
+          <t>Data Platform Architect</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Intuit</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>Atlanta, GA, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D31" t="n">
@@ -1501,7 +1501,7 @@
       </c>
       <c r="E31" t="inlineStr">
         <is>
-          <t>AWS, RDS, BigQuery, Scala, PostgreSQL, MySQL, Splunk, CI/CD, Jenkins, Terraform</t>
+          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
         </is>
       </c>
       <c r="F31" t="inlineStr">
@@ -1511,24 +1511,24 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7f60289bd7b154e2</t>
+          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
         </is>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Senior Developer</t>
+          <t>Forward Deployed Software Engineer (FDE)</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Centerprism</t>
+          <t>Zebra Technologies</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>St. Louis, MO, US USA</t>
+          <t>Holtsville, NY, US USA</t>
         </is>
       </c>
       <c r="D32" t="n">
@@ -1536,42 +1536,42 @@
       </c>
       <c r="E32" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, SQL Server, PostgreSQL, MySQL, MongoDB, NoSQL, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
         </is>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b3e11011f10bd71</t>
+          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Data Platform Architect</t>
+          <t>Software Engineer III - Cloud Data Platform</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Guidewire</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>San Mateo, CA, US USA</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E33" t="inlineStr">
         <is>
-          <t>AWS, Redshift, RDS, Azure, Databricks, Unity Catalog, GCP, BigQuery, Spark, Scala</t>
+          <t>AWS, RDS, Azure, GCP, Hadoop, Hive, Spark, Scala, Kafka, CI/CD</t>
         </is>
       </c>
       <c r="F33" t="inlineStr">
@@ -1581,67 +1581,67 @@
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a0600fe838e8fd40</t>
+          <t>https://www.indeed.com/viewjob?jk=26ac8e996e1bb5d6</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Forward Deployed Software Engineer (FDE)</t>
+          <t>Associate Cloud &amp; DevOps Engineer</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Zebra Technologies</t>
+          <t>First Orion</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>Holtsville, NY, US USA</t>
+          <t>North Little Rock, AR, US USA</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, BigQuery, Scala, PostgreSQL, MySQL, MongoDB, NoSQL</t>
+          <t>AWS, Kinesis, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=cb34fa941aa1af4f</t>
+          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Software Development Engineer II</t>
+          <t>AI Solutions Architect | US</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>Cuesta Partners</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>12.5</v>
+        <v>11.8</v>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Docker</t>
+          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
@@ -1651,24 +1651,24 @@
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=025ebe3ef0840042</t>
+          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Associate Cloud &amp; DevOps Engineer</t>
+          <t>Software Engineer III</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>First Orion</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>North Little Rock, AR, US USA</t>
+          <t>Columbus, OH, US USA</t>
         </is>
       </c>
       <c r="D36" t="n">
@@ -1676,7 +1676,7 @@
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>AWS, Kinesis, S3, SQS, IAM, RDS, Scala, DynamoDB, CI/CD, Terraform</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
@@ -1686,24 +1686,24 @@
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=6f4ff182033422db</t>
+          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Software Engineer III</t>
+          <t>Application Developer</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Applied Medical</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>Columbus, OH, US USA</t>
+          <t>Rancho Santa Margarita, CA, US USA</t>
         </is>
       </c>
       <c r="D37" t="n">
@@ -1711,104 +1711,104 @@
       </c>
       <c r="E37" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, Kafka, NoSQL, Data Modeling, CI/CD</t>
+          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
         </is>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4beac6cc3645a53b</t>
+          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Application Developer</t>
+          <t>Senior Data Engineer</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Applied Medical</t>
+          <t>AMH</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>Rancho Santa Margarita, CA, US USA</t>
+          <t>Las Vegas, NV, US USA</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E38" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, YARN, SQL Server, PostgreSQL, Azure Cosmos DB, NoSQL, CI/CD, GitHub Actions</t>
+          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
         </is>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a4fc216d4e8e348b</t>
+          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>AI Solutions Architect | US</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Cuesta Partners</t>
+          <t>Cronisys IT LLC</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Dallas, TX, US USA</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>11.8</v>
+        <v>11.1</v>
       </c>
       <c r="E39" t="inlineStr">
         <is>
-          <t>AWS, Azure, Databricks, GCP, BigQuery, Vertex AI, Scala, Snowflake, Data Modeling, MLflow</t>
+          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
         </is>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=96a29f61f02164cc</t>
+          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Senior Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>AMH</t>
+          <t>One Call</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Las Vegas, NV, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D40" t="n">
@@ -1816,34 +1816,34 @@
       </c>
       <c r="E40" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Spark, Scala, Kafka, NoSQL, Data Modeling, Power BI</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fcc108d020014d64</t>
+          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Full Stack Engineer</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Cronisys IT LLC</t>
+          <t>Avature</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>Dallas, TX, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D41" t="n">
@@ -1851,34 +1851,34 @@
       </c>
       <c r="E41" t="inlineStr">
         <is>
-          <t>AWS, Azure, Hadoop, Hive, Spark, Scala, Oracle, SQL Server, ETL, Talend</t>
+          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-20</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=7b7d3c5854895a0d</t>
+          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Cloud Engineer</t>
         </is>
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>One Call</t>
+          <t>Millennium Management</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Miami, FL, US USA</t>
         </is>
       </c>
       <c r="D42" t="n">
@@ -1886,34 +1886,34 @@
       </c>
       <c r="E42" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
         </is>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=454dc6c270b9d674</t>
+          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Full Stack Engineer</t>
+          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Avature</t>
+          <t>Medica Services Company LLC</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Minnetonka, MN, US USA</t>
         </is>
       </c>
       <c r="D43" t="n">
@@ -1921,34 +1921,34 @@
       </c>
       <c r="E43" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Azure, GCP, Scala, Kafka, SQL Server, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
         </is>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-20</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=d8ad65ea2360e07e</t>
+          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Cloud Engineer</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>Millennium Management</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>Miami, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D44" t="n">
@@ -1956,7 +1956,7 @@
       </c>
       <c r="E44" t="inlineStr">
         <is>
-          <t>AWS, S3, ECS, IAM, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Kubernetes</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F44" t="inlineStr">
@@ -1966,24 +1966,24 @@
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=76545a7a26014492</t>
+          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Senior Platform &amp; Integration Engineer (Kafka)</t>
+          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Medica Services Company LLC</t>
+          <t>OEConnection</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>Minnetonka, MN, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D45" t="n">
@@ -1991,7 +1991,7 @@
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, Kafka, Splunk, CI/CD, GitHub Actions, Azure DevOps, Terraform</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
@@ -2001,19 +2001,19 @@
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1a1e479ebfe2163b</t>
+          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Clinical Data Engineer (Application Engineer)</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>Oregon Health &amp; Science University</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -2026,34 +2026,34 @@
       </c>
       <c r="E46" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
         </is>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=024ce94c4237b353</t>
+          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Senior Platform Engineer (Cloud &amp; AI Platform)- Remote within US</t>
+          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>OEConnection</t>
+          <t>H&amp;R Block</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>MO, US USA</t>
         </is>
       </c>
       <c r="D47" t="n">
@@ -2061,34 +2061,34 @@
       </c>
       <c r="E47" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Jenkins, GitHub Actions, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
         </is>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=e08d2c63dac884c6</t>
+          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
         </is>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Clinical Data Engineer (Application Engineer)</t>
+          <t>Senior Software Engineer — Cloud Services &amp; API Platform (C#/Azure Track)</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>Oregon Health &amp; Science University</t>
+          <t>Simpson Strong-Tie</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D48" t="n">
@@ -2096,34 +2096,34 @@
       </c>
       <c r="E48" t="inlineStr">
         <is>
-          <t>Azure, Medallion Architecture, Spark, PySpark, Scala, SQL Server, Dimensional Modeling, ETL, Azure DevOps, Airflow</t>
+          <t>AWS, RDS, Azure, Scala, Data Modeling, CI/CD, GitHub Actions, Azure DevOps, Terraform, Docker</t>
         </is>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=4baa56a62cb41945</t>
+          <t>https://www.indeed.com/viewjob?jk=b066ce08bf22f47c</t>
         </is>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Senior Software Engineer-Data Operations (Databricks/AI)</t>
+          <t>Artificial Intelligence Architect</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>H&amp;R Block</t>
+          <t>M2S Group</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>MO, US USA</t>
+          <t>Highland Park, IL, US USA</t>
         </is>
       </c>
       <c r="D49" t="n">
@@ -2131,34 +2131,34 @@
       </c>
       <c r="E49" t="inlineStr">
         <is>
-          <t>AWS, Azure, Data Factory, Databricks, Scala, Data Modeling, ETL, ELT, DataOps, CI/CD</t>
+          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=22eb530ec4c57c3c</t>
+          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
         </is>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Artificial Intelligence Architect</t>
+          <t>Solutions Architect</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>M2S Group</t>
+          <t>BGE, Inc</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>Highland Park, IL, US USA</t>
+          <t>Austin, TX, US USA</t>
         </is>
       </c>
       <c r="D50" t="n">
@@ -2166,7 +2166,7 @@
       </c>
       <c r="E50" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Spark, Scala, MLOps, MLflow, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
         </is>
       </c>
       <c r="F50" t="inlineStr">
@@ -2176,7 +2176,7 @@
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=dde1cd623d007554</t>
+          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
         </is>
       </c>
     </row>
@@ -2193,7 +2193,7 @@
       </c>
       <c r="C51" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D51" t="n">
@@ -2211,7 +2211,7 @@
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=54c4f37450aa9007</t>
+          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
         </is>
       </c>
     </row>
@@ -2228,7 +2228,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Frisco, TX, US USA</t>
         </is>
       </c>
       <c r="D52" t="n">
@@ -2246,24 +2246,24 @@
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=1ed66eb1c43b3061</t>
+          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Solutions Architect</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>BGE, Inc</t>
+          <t>PURE Insurance</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
         <is>
-          <t>Frisco, TX, US USA</t>
+          <t>White Plains, NY, US USA</t>
         </is>
       </c>
       <c r="D53" t="n">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="E53" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, Data Modeling, ETL, Power BI, Tableau</t>
+          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
         </is>
       </c>
       <c r="F53" t="inlineStr">
@@ -2281,24 +2281,24 @@
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=b4f5eb1da717e31e</t>
+          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Senior Pre-Sales Solution Architect</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>PURE Insurance</t>
+          <t>Blue Orange Digital</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
         <is>
-          <t>White Plains, NY, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D54" t="n">
@@ -2306,7 +2306,7 @@
       </c>
       <c r="E54" t="inlineStr">
         <is>
-          <t>AWS, ECS, RDS, Databricks, Scala, CI/CD, Terraform, Docker, AKS, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
         </is>
       </c>
       <c r="F54" t="inlineStr">
@@ -2316,24 +2316,24 @@
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=2b7ea8b8e5406480</t>
+          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Senior Pre-Sales Solution Architect</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Blue Orange Digital</t>
+          <t>LexisNexis Risk Solutions</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
         <is>
-          <t>New York, NY, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D55" t="n">
@@ -2341,7 +2341,7 @@
       </c>
       <c r="E55" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Unity Catalog, GCP, Spark, Snowflake, ELT, dbt</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F55" t="inlineStr">
@@ -2351,24 +2351,24 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=148c58d976f8aa98</t>
+          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>SW Engineer - Sr. Consultant level</t>
+          <t>Senior Software Engineer II</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Visa</t>
+          <t>RELX Group</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
         <is>
-          <t>Austin, TX, US USA</t>
+          <t>GA, US USA</t>
         </is>
       </c>
       <c r="D56" t="n">
@@ -2376,34 +2376,34 @@
       </c>
       <c r="E56" t="inlineStr">
         <is>
-          <t>RDS, Scala, Kafka, Oracle, MySQL, NoSQL, Jenkins, Maven, Docker, Kubernetes</t>
+          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
         </is>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>2026-07-22</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=a9957a07b3110fb6</t>
+          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Integration Developer</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>LexisNexis Risk Solutions</t>
+          <t>Kyocera Document Solutions America, Inc.</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Fairfield, NJ, US USA</t>
         </is>
       </c>
       <c r="D57" t="n">
@@ -2411,34 +2411,34 @@
       </c>
       <c r="E57" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
         </is>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=77de33f1323a932a</t>
+          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t>Senior Software Engineer II</t>
+          <t>Software Engineer III - Full Stack ReactJS, Java, Python, AWS + Monday.com Platform</t>
         </is>
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>RELX Group</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
         <is>
-          <t>GA, US USA</t>
+          <t>Plano, TX, US USA</t>
         </is>
       </c>
       <c r="D58" t="n">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="E58" t="inlineStr">
         <is>
-          <t>AWS, Azure, Scala, SQL Server, MySQL, ETL, CI/CD, Jenkins, GitHub Actions, Docker</t>
+          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
         </is>
       </c>
       <c r="F58" t="inlineStr">
@@ -2456,24 +2456,24 @@
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=fca0033255b9f7dc</t>
+          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Senior Architect</t>
+          <t>Data Engineer</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>United Concordia Dental</t>
+          <t>Orion Innovation</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
         <is>
-          <t>PA, US USA</t>
+          <t>Montvale, NJ, US USA</t>
         </is>
       </c>
       <c r="D59" t="n">
@@ -2481,7 +2481,7 @@
       </c>
       <c r="E59" t="inlineStr">
         <is>
-          <t>AWS, S3, RDS, Google Cloud Platform, GCP, Hadoop, Scala, Oracle, CI/CD, Terraform</t>
+          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
         </is>
       </c>
       <c r="F59" t="inlineStr">
@@ -2491,137 +2491,137 @@
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=894c050699a8cfaa</t>
+          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Data Engineer</t>
+          <t>Sr. Analytics Engineer</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Orion Innovation</t>
+          <t>Axogen</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>Montvale, NJ, US USA</t>
+          <t>Tampa, FL, US USA</t>
         </is>
       </c>
       <c r="D60" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E60" t="inlineStr">
         <is>
-          <t>Azure, Data Factory, Databricks, Spark, PySpark, Scala, Oracle, SQL Server, ETL, ELT</t>
+          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
         </is>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=3e0ce9990f1abbe3</t>
+          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Software Development Engineer II - Gen AI and Innovation Team</t>
+          <t>DERMS Data Architect &amp; Integration</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>GM Financial</t>
+          <t>GE Vernova</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
         <is>
-          <t>Arlington, TX, US USA</t>
+          <t>Bellevue, WA, US USA</t>
         </is>
       </c>
       <c r="D61" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E61" t="inlineStr">
         <is>
-          <t>Azure, Scala, Oracle, SQL Server, NoSQL, Jenkins, Azure DevOps, Maven, Terraform, Jenkins</t>
+          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
         </is>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=ebdcb0ba13a35657</t>
+          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Integration Developer</t>
+          <t>Senior AI Engineer</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Kyocera Document Solutions America, Inc.</t>
+          <t>Mastercard</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
         <is>
-          <t>Fairfield, NJ, US USA</t>
+          <t>O'Fallon, MO, US USA</t>
         </is>
       </c>
       <c r="D62" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E62" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Cloud Storage, Scala, Oracle, SQL Server, ETL, ELT, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
         </is>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2026-07-24</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c00d2e785c66cbb4</t>
+          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t>Software Engineer III - Frontend, Monday.com, AWS</t>
+          <t>Java Application Architect</t>
         </is>
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>BV Teck</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
         <is>
-          <t>Plano, TX, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D63" t="n">
-        <v>11.1</v>
+        <v>10.4</v>
       </c>
       <c r="E63" t="inlineStr">
         <is>
-          <t>AWS, Lambda, S3, API Gateway, ECS, RDS, Databricks, Scala, CI/CD, Jenkins</t>
+          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
         </is>
       </c>
       <c r="F63" t="inlineStr">
@@ -2631,24 +2631,24 @@
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=8e21285074de6c55</t>
+          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Sr. Analytics Engineer</t>
+          <t>Senior Systems &amp; Backend Engineer</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Axogen</t>
+          <t>nan</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
         <is>
-          <t>Tampa, FL, US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D64" t="n">
@@ -2656,7 +2656,7 @@
       </c>
       <c r="E64" t="inlineStr">
         <is>
-          <t>RDS, Azure, Databricks, Scala, Data Modeling, Dimensional Modeling, Fact Tables, Power BI, CI/CD, Azure DevOps</t>
+          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F64" t="inlineStr">
@@ -2666,24 +2666,24 @@
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=24d477b9eaa3792d</t>
+          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>DERMS Data Architect &amp; Integration</t>
+          <t>IT Cloud Architect</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>GE Vernova</t>
+          <t>Hackensack Meridian Health</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
         <is>
-          <t>Bellevue, WA, US USA</t>
+          <t>Iselin, NJ, US USA</t>
         </is>
       </c>
       <c r="D65" t="n">
@@ -2691,34 +2691,34 @@
       </c>
       <c r="E65" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, GCP, Snowflake, Oracle, SQL Server, Dimensional Modeling, ETL, Power BI</t>
+          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
         </is>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=381bad2f60317342</t>
+          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Senior AI Engineer</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Mastercard</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
         <is>
-          <t>O'Fallon, MO, US USA</t>
+          <t>US USA</t>
         </is>
       </c>
       <c r="D66" t="n">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="E66" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Vertex AI, Scala, MLOps, MLflow, Git</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F66" t="inlineStr">
@@ -2736,19 +2736,19 @@
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=935ece4128fe6f9f</t>
+          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Java Application Architect</t>
+          <t>Business Informatics Support Data Engineer</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>BV Teck</t>
+          <t>Trillium Health Resources</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -2761,7 +2761,7 @@
       </c>
       <c r="E67" t="inlineStr">
         <is>
-          <t>AWS, Azure, GCP, Kafka, Oracle, SQL Server, PostgreSQL, MySQL, CI/CD, Docker</t>
+          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
         </is>
       </c>
       <c r="F67" t="inlineStr">
@@ -2771,24 +2771,24 @@
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=961ed4e278a33edd</t>
+          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Senior Systems &amp; Backend Engineer</t>
+          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>nan</t>
+          <t>JPMorganChase</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>Jersey City, NJ, US USA</t>
         </is>
       </c>
       <c r="D68" t="n">
@@ -2796,7 +2796,7 @@
       </c>
       <c r="E68" t="inlineStr">
         <is>
-          <t>AWS, SQS, SNS, Scala, Kafka, PostgreSQL, CI/CD, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
         </is>
       </c>
       <c r="F68" t="inlineStr">
@@ -2806,24 +2806,24 @@
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=844436f2f472f5b1</t>
+          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>IT Cloud Architect</t>
+          <t>Quality Assurance Specialist</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Hackensack Meridian Health</t>
+          <t>RELI Group Inc</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
         <is>
-          <t>Iselin, NJ, US USA</t>
+          <t>Baltimore, MD, US USA</t>
         </is>
       </c>
       <c r="D69" t="n">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="E69" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Google Cloud Platform, GCP, Scala, CI/CD, Terraform, Docker, Kubernetes</t>
+          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
         </is>
       </c>
       <c r="F69" t="inlineStr">
@@ -2841,24 +2841,24 @@
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c748d45f480e02e9</t>
+          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Data Scientist</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Great Gray Trust Company</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>US USA</t>
+          <t>Remote, US USA</t>
         </is>
       </c>
       <c r="D70" t="n">
@@ -2866,7 +2866,7 @@
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
@@ -2876,24 +2876,24 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=c1bc5a017b98965e</t>
+          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Business Informatics Support Data Engineer</t>
+          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Trillium Health Resources</t>
+          <t>Databricks</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
         <is>
-          <t>Remote, US USA</t>
+          <t>New York, NY, US USA</t>
         </is>
       </c>
       <c r="D71" t="n">
@@ -2901,34 +2901,34 @@
       </c>
       <c r="E71" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Databricks, Hadoop, Scala, Snowflake, SQL Server, NoSQL, Power BI</t>
+          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
         </is>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>2026-07-24</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=61b3b18503d4acec</t>
+          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Data Engineer III - (Pyspark/databricks/Mongo/Sql/Python)</t>
+          <t>Software Engineer – Full Stack</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>JPMorganChase</t>
+          <t>Empower Pharmacy</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
         <is>
-          <t>Jersey City, NJ, US USA</t>
+          <t>Houston, TX, US USA</t>
         </is>
       </c>
       <c r="D72" t="n">
@@ -2936,7 +2936,7 @@
       </c>
       <c r="E72" t="inlineStr">
         <is>
-          <t>AWS, Lambda, ECS, RDS, Databricks, Spark, PySpark, Scala, NoSQL, ETL</t>
+          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
         </is>
       </c>
       <c r="F72" t="inlineStr">
@@ -2946,24 +2946,24 @@
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>https://www.indeed.com/viewjob?jk=820ae5b00199f1e8</t>
+          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Software Engineer – Full Stack</t>
+          <t>Full Stack Developer</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Empower Pharmacy</t>
+          <t>LEADER BANK</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
         <is>
-          <t>Houston, TX, US USA</t>
+          <t>Arlington, MA, US USA</t>
         </is>
       </c>
       <c r="D73" t="n">
@@ -2971,7 +2971,7 @@
       </c>
       <c r="E73" t="inlineStr">
         <is>
-          <t>AWS, RDS, Azure, Scala, CI/CD, Azure DevOps, Terraform, Docker, Kubernetes, Git</t>
+          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, CI/CD, Git, CloudWatch</t>
         </is>
       </c>
       <c r="F73" t="inlineStr">
@@ -2980,146 +2980,6 @@
         </is>
       </c>
       <c r="G73" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=e06173fc3c6ce8f8</t>
-        </is>
-      </c>
-    </row>
-    <row r="74">
-      <c r="A74" t="inlineStr">
-        <is>
-          <t>Quality Assurance Specialist</t>
-        </is>
-      </c>
-      <c r="B74" t="inlineStr">
-        <is>
-          <t>RELI Group Inc</t>
-        </is>
-      </c>
-      <c r="C74" t="inlineStr">
-        <is>
-          <t>Baltimore, MD, US USA</t>
-        </is>
-      </c>
-      <c r="D74" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E74" t="inlineStr">
-        <is>
-          <t>AWS, Redshift, S3, RDS, Databricks, Scala, Oracle, SQL Server, PostgreSQL, MySQL</t>
-        </is>
-      </c>
-      <c r="F74" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G74" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=3691bd3a3b5f022b</t>
-        </is>
-      </c>
-    </row>
-    <row r="75">
-      <c r="A75" t="inlineStr">
-        <is>
-          <t>Data Scientist</t>
-        </is>
-      </c>
-      <c r="B75" t="inlineStr">
-        <is>
-          <t>Great Gray Trust Company</t>
-        </is>
-      </c>
-      <c r="C75" t="inlineStr">
-        <is>
-          <t>Remote, US USA</t>
-        </is>
-      </c>
-      <c r="D75" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E75" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, Scala, ETL, Docker, SonarQube, Git, Python</t>
-        </is>
-      </c>
-      <c r="F75" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G75" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=6d12b3ac28ec908f</t>
-        </is>
-      </c>
-    </row>
-    <row r="76">
-      <c r="A76" t="inlineStr">
-        <is>
-          <t>Sr. Forward Deployed Engineer (FDE) - Healthcare &amp; Life Sciences</t>
-        </is>
-      </c>
-      <c r="B76" t="inlineStr">
-        <is>
-          <t>Databricks</t>
-        </is>
-      </c>
-      <c r="C76" t="inlineStr">
-        <is>
-          <t>New York, NY, US USA</t>
-        </is>
-      </c>
-      <c r="D76" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E76" t="inlineStr">
-        <is>
-          <t>AWS, RDS, Azure, Databricks, GCP, Spark, Scala, ELT, MLOps, MLflow</t>
-        </is>
-      </c>
-      <c r="F76" t="inlineStr">
-        <is>
-          <t>2026-07-23</t>
-        </is>
-      </c>
-      <c r="G76" t="inlineStr">
-        <is>
-          <t>https://www.indeed.com/viewjob?jk=81cea3875bd25185</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" t="inlineStr">
-        <is>
-          <t>Full Stack Developer</t>
-        </is>
-      </c>
-      <c r="B77" t="inlineStr">
-        <is>
-          <t>LEADER BANK</t>
-        </is>
-      </c>
-      <c r="C77" t="inlineStr">
-        <is>
-          <t>Arlington, MA, US USA</t>
-        </is>
-      </c>
-      <c r="D77" t="n">
-        <v>10.4</v>
-      </c>
-      <c r="E77" t="inlineStr">
-        <is>
-          <t>AWS, Lambda, S3, RDS, Scala, PostgreSQL, MySQL, CI/CD, Git, CloudWatch</t>
-        </is>
-      </c>
-      <c r="F77" t="inlineStr">
-        <is>
-          <t>2026-07-24</t>
-        </is>
-      </c>
-      <c r="G77" t="inlineStr">
         <is>
           <t>https://www.indeed.com/viewjob?jk=6a9fb68922a90c5c</t>
         </is>
